--- a/Тематика для рассылки/Готовые файлы/03_Проверка_источников.xlsx
+++ b/Тематика для рассылки/Готовые файлы/03_Проверка_источников.xlsx
@@ -15,11 +15,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Расхождения'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Расхождения'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Расхождения'!$A$1:$E$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Все связи'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Все связи'!$A$1:$G$337</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Все связи'!$A$1:$G$332</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Объединённые названия'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Объединённые названия'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Объединённые названия'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Похожие, оставлены отдельно'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Похожие, оставлены отдельно'!$A$1:$C$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Документы'!$1:$5</definedName>
@@ -404,8 +404,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Issues" displayName="Issues" ref="A5:E29" headerRowCount="1">
-  <autoFilter ref="A5:E29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Issues" displayName="Issues" ref="A5:E17" headerRowCount="1">
+  <autoFilter ref="A5:E17"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Программа"/>
     <tableColumn id="2" name="Тема УТП"/>
@@ -418,8 +418,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Mappings" displayName="Mappings" ref="A5:G337" headerRowCount="1">
-  <autoFilter ref="A5:G337"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Mappings" displayName="Mappings" ref="A5:G332" headerRowCount="1">
+  <autoFilter ref="A5:G332"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Код темы"/>
     <tableColumn id="2" name="Тема каталога"/>
@@ -434,8 +434,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Aliases" displayName="Aliases" ref="A5:C15" headerRowCount="1">
-  <autoFilter ref="A5:C15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Aliases" displayName="Aliases" ref="A5:C13" headerRowCount="1">
+  <autoFilter ref="A5:C13"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Исходный вариант"/>
     <tableColumn id="2" name="Название каталога"/>
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -828,27 +828,27 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Архитектура SIEM. Установка и настройка основных компонентов</t>
+          <t>Классификация информационной системы</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Название отличается</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Архитектура, назначение NT SIEM. Установка и настройка основных компонентов (1 час практические занятия)</t>
+          <t>Тема 3. Практикум (8 часов практические занятия).</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Названия в УТП и обновлённой программе различаются. Приведён фактический текст соответствующего раздела программы.</t>
+          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Классификация информационной системы</t>
+          <t>Обследование и анализ исходных данных на информационную систему</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -882,73 +882,81 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Наглядная демонстрация рисков для предприятия на базе киберполигона при ошибках настройки СЗИ или автоматизированных систем киберцентра</t>
+          <t>Определение перечня и разработка локальных правовых актов, регламентирующих вопросы защиты информации</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Описание не найдено</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr"/>
+          <t>Общий практикум</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Тема 9. Практикум (6 часов практические занятия).</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Тема есть в УТП, но отдельное описание не найдено и в обновлённой программе ОКБО.</t>
+          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Назначение NT-SIEM, компоненты системы, направления развития, потоки данных. Установка системы. Написание правил</t>
+          <t>Подготовка исходных данных к проведению аттестации системы защиты информации</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Сопоставление фрагментов</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Архитектура, назначение NT SIEM. Установка и настройка основных компонентов (1 час практические занятия) / Тема 5. Нормализация событий, корреляция, обработка ложных событий (1 час практические занятия).</t>
+          <t>Тема 9. Практикум (6 часов практические занятия).</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Содержание составлено из указанных фрагментов обновлённой программы. Название УТП отличается; соответствие требует проверки организатором.</t>
+          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr"/>
+          <t>АУРИК</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Проведение оценки рисков кибербезопасности</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Добавлено из программы</t>
+          <t>Название отличается</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Тема 5. Нормализация событий, корреляция, обработка ложных событий (1 час практические занятия).</t>
+          <t>Тема 3. Проведение оценки рисков кибербезопасности в организации (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Тема выделена в обновлённой программе отдельно. В текущем УТП нет отдельной строки с таким названием; источник — программа.</t>
+          <t>Названия в УТП и программе различаются; ниже приведён фактический текст соответствующего раздела программы.</t>
         </is>
       </c>
     </row>
@@ -960,7 +968,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Обследование и анализ исходных данных на информационную систему</t>
+          <t>Разработка политики информационной безопасности</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -987,7 +995,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Определение перечня и разработка локальных правовых актов, регламентирующих вопросы защиты информации</t>
+          <t>Разработка программы и методики аттестации</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -997,7 +1005,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Тема 9. Практикум (6 часов практические занятия).</t>
+          <t>Тема 1. Практикум (6 часов практические занятия).</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1009,23 +1017,27 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Оценка эффективности защищенности. Оценка степени зрелости компании, оценка правильности назначения ответственных лиц на предприятии и выстроенных бизнес-процессов. Аудит информационной безопасности и ее составляющие. Тесты на проникновение</t>
+          <t>Разработка структурной и логической схем системы защиты информации</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Описание не найдено</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr"/>
+          <t>Общий практикум</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Тема 9. Практикум (6 часов практические занятия).</t>
+        </is>
+      </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Тема есть в УТП, но отдельное описание не найдено и в обновлённой программе ОКБО.</t>
+          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1049,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Подготовка исходных данных к проведению аттестации системы защиты информации</t>
+          <t>Разработка технического задания на создание системы защиты информации</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1047,7 +1059,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Тема 9. Практикум (6 часов практические занятия).</t>
+          <t>Тема 3. Практикум (8 часов практические занятия).</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1059,27 +1071,27 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Подключение источника, нормализация событий, корреляция, обработка ложных событий</t>
+          <t>Разработка технического отчета и протокола испытаний</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Сопоставление фрагментов</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Подключение различных источников событий (2 часа практические занятия). / Тема 5. Нормализация событий, корреляция, обработка ложных событий (1 час практические занятия).</t>
+          <t>Тема 1. Практикум (6 часов практические занятия).</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Содержание составлено из указанных фрагментов обновлённой программы. Название УТП отличается; соответствие требует проверки организатором.</t>
+          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
         </is>
       </c>
     </row>
@@ -1089,32 +1101,36 @@
           <t>ОКБО</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Реагирование на киберинциденты. Подготовительные, организационные и практические мероприятия</t>
+        </is>
+      </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Добавлено из программы</t>
+          <t>Название отличается</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Подключение различных источников событий (2 часа практические занятия).</t>
+          <t>Тема 1. Реагирование на КИ. Подготовительные, организационные и практические мероприятия (1 час лекции, 3 часа практические занятия).</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Тема выделена в обновлённой программе отдельно. В текущем УТП нет отдельной строки с таким названием; источник — программа.</t>
+          <t>В УТП используется полное название «киберинциденты», а в программе — сокращение «КИ». Описание взято из соответствующей темы программы.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Проведение оценки рисков кибербезопасности</t>
+          <t>Криптографические средства защиты информации</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1124,328 +1140,12 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Проведение оценки рисков кибербезопасности в организации (4 часа практические занятия).</t>
+          <t>Тема 1. Средства криптографической защиты информации (2 часа лекции).</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Названия в УТП и программе различаются; ниже приведён фактический текст соответствующего раздела программы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>ПСАЭ</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Разработка политики информационной безопасности</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Общий практикум</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Тема 3. Практикум (8 часов практические занятия).</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>ПСАЭ</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Разработка программы и методики аттестации</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Общий практикум</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Тема 1. Практикум (6 часов практические занятия).</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>ПСАЭ</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Разработка структурной и логической схем системы защиты информации</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Общий практикум</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Тема 9. Практикум (6 часов практические занятия).</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>ПСАЭ</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Разработка технического задания на создание системы защиты информации</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Общий практикум</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Тема 3. Практикум (8 часов практические занятия).</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>ПСАЭ</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Разработка технического отчета и протокола испытаний</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Общий практикум</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Тема 1. Практикум (6 часов практические занятия).</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>В программе тема перечислена как задание общего практикума. Отдельного развёрнутого описания нет; приведён общий контекст, включающий другие задания.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Реагирование на киберинциденты. Подготовительные, организационные и практические мероприятия</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Название отличается</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Тема 1. Реагирование на КИ. Подготовительные, организационные и практические мероприятия (1 час лекции, 3 часа практические занятия).</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Названия в УТП и обновлённой программе различаются. Приведён фактический текст соответствующего раздела программы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Базовая конфигурация SOAR: написания плейбука, отработка плейбука, процесс автоматизации</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Название отличается</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Тема 1. Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования (3 часа практические занятия).</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>Названия в УТП и обновлённой программе различаются. Приведён фактический текст соответствующего раздела программы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr"/>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Добавлено из программы</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Тема 3. Совместное функционирование систем SIEM, SOAR и TIP (2 часа лекции).</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Тема выделена в обновлённой программе отдельно. В текущем УТП нет отдельной строки с таким названием; источник — программа.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Базовая конфигурация TIP</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Название отличается</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Тема 2. Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук (2 часа практические занятия).</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>Названия в УТП и обновлённой программе различаются. Приведён фактический текст соответствующего раздела программы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>КО</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Криптографические средства защиты информации</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Название отличается</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Тема 1. Средства криптографической защиты информации (2 часа лекции).</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Названия в УТП и программе различаются; ниже приведён фактический текст соответствующего раздела программы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Типы источников событий информационной безопасности. Теоретические аспекты подключения источников событий ИБ в SIEM (события Windows/Linux, СУБД, телекоммуникационного оборудования, антивируса, NGFW с функцией ips)</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Название отличается</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Тема 3. Типы источников событий информационной безопасности. Теоретические аспекты подключения источников событий ИБ к SIEM-системе (события Windows/Linux, СУБД, телекоммуникационного оборудования, антивируса, NGFW с функцией ips) (1 час лекции).</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>Названия в УТП и обновлённой программе различаются. Приведён фактический текст соответствующего раздела программы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Цель и задачи XDR, его преимущества</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Описание не найдено</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr"/>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Тема есть в УТП, но отдельное описание не найдено и в обновлённой программе ОКБО.</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G337"/>
+  <dimension ref="A1:G332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1797,12 +1497,12 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. SIEM-системы. Краткий обзор существующих решений. Сертифицированные open-source и коммерческие решения в Республике Беларусь (2 часа лекции).</t>
+          <t>Тема 1. SIEM-системы. Краткий обзор существующих решений. Сертифицированные open-source и коммерческие решения в Республике Беларусь (2 часа лекции).</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 28</t>
+          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 27</t>
         </is>
       </c>
     </row>
@@ -2157,12 +1857,12 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Архитектура SIEM. Установка и настройка основных компонентов</t>
+          <t>Архитектура, назначение NT SIEM. Установка и настройка основных компонентов</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Название отличается</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -2172,7 +1872,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 29</t>
+          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 28</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2279,7 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Управление доступом и аутентификация; таблица 2, строка 24</t>
+          <t>Управление доступом и аутентификация; таблица 2, строка 23</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2316,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Отработка практических заданий на базе киберполигона; таблица 2, строка 46</t>
+          <t>Отработка практических заданий на базе киберполигона; таблица 2, строка 45</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3517,12 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Государственное регулирование деятельности в сфере обеспечения кибербезопасности</t>
+          <t>Государственное регулирование деятельности в области обеспечения кибербезопасности в Республике Беларусь</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3832,12 +3532,12 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Государственное регулирование деятельности в сфере обеспечения кибербезопасности (3 часа лекции).</t>
+          <t>Тема 1. Государственное регулирование деятельности в области обеспечения кибербезопасности в Республике Беларусь (4 часа лекции).</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Нормативное правовое регулирование вопросов кибербезопасности в Республике Беларусь; таблица 2, строка 7</t>
+          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 6</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3554,7 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -3874,7 +3574,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 6</t>
+          <t>Основы обеспечения кибербезопасности; таблица 2, строка 18</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3591,7 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -3911,7 +3611,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности; таблица 2, строка 18</t>
+          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 6</t>
         </is>
       </c>
     </row>
@@ -3928,12 +3628,12 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Государственное регулирование деятельности в области обеспечения кибербезопасности в Республике Беларусь</t>
+          <t>Государственное регулирование деятельности в сфере обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -3943,12 +3643,12 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Государственное регулирование деятельности в области обеспечения кибербезопасности в Республике Беларусь (4 часа лекции).</t>
+          <t>Тема 2. Государственное регулирование деятельности в сфере обеспечения кибербезопасности (3 часа лекции).</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 6</t>
+          <t>Нормативное правовое регулирование вопросов кибербезопасности в Республике Беларусь; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
@@ -6131,7 +5831,7 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>Управление доступом и аутентификация; таблица 2, строка 23</t>
+          <t>Управление доступом и аутентификация; таблица 2, строка 22</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6319,12 @@
     <row r="143" ht="64" customHeight="1">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>T-08E524F3</t>
+          <t>T-B1B43BE0</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>Наглядная демонстрация рисков для предприятия на базе киберполигона при ошибках настройки СЗИ или автоматизированных систем киберцентра</t>
+          <t>Назначение и функции ЦКБ, организация процессов в ЦКБ</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
@@ -6634,77 +6334,81 @@
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Наглядная демонстрация рисков для предприятия на базе киберполигона при ошибках настройки СЗИ или автоматизированных систем киберцентра</t>
+          <t>Назначение и функции ЦКБ, организация процессов в ЦКБ</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>Описание не найдено</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="inlineStr"/>
+          <t>Точное соответствие</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>Тема 1. Назначение и функции ЦКБ, организация процессов в ЦКБ (1 час лекции).</t>
+        </is>
+      </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Отработка практических заданий на базе киберполигона; таблица 2, строка 47</t>
+          <t>Основные функции центров обеспечения кибербезопасности и реагирования на киберинциденты объектов информационной инфраструктуры государственных органов и иных организаций (ЦКБ), процессы информационной безопасности; таблица 2, строка 14</t>
         </is>
       </c>
     </row>
     <row r="144" ht="64" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>T-7CBDE232</t>
+          <t>T-DBE021AA</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Назначение NT-SIEM, компоненты системы, направления развития, потоки данных. Установка системы. Написание правил</t>
+          <t>Написание скриптов автоматического реагирования (Python, Bash)</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Назначение NT-SIEM, компоненты системы, направления развития, потоки данных. Установка системы. Написание правил</t>
+          <t>Написание скриптов автоматического реагирования (Python, Bash)</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Сопоставление фрагментов</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Архитектура, назначение NT SIEM. Установка и настройка основных компонентов (1 час практические занятия) / Тема 5. Нормализация событий, корреляция, обработка ложных событий (1 час практические занятия).</t>
+          <t>Тема 2. Написание скриптов автоматического реагирования (Python, Bash) (1 час лекции).</t>
         </is>
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 31</t>
+          <t>Сканирование уязвимостей, скрипты реагирования, скрипты для сбора логов; таблица 2, строка 30</t>
         </is>
       </c>
     </row>
     <row r="145" ht="64" customHeight="1">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>T-B1B43BE0</t>
+          <t>T-E5761E9C</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>Назначение и функции ЦКБ, организация процессов в ЦКБ</t>
+          <t>Написание скриптов для сбора и анализа логов (Python)</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Назначение и функции ЦКБ, организация процессов в ЦКБ</t>
+          <t>Написание скриптов для сбора и анализа логов (Python)</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -6714,34 +6418,34 @@
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Назначение и функции ЦКБ, организация процессов в ЦКБ (1 час лекции).</t>
+          <t>Тема 3. Написание скриптов для сбора и анализа логов (Python) (2 часа лекции).</t>
         </is>
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>Основные функции центров обеспечения кибербезопасности и реагирования на киберинциденты объектов информационной инфраструктуры государственных органов и иных организаций (ЦКБ), процессы информационной безопасности; таблица 2, строка 14</t>
+          <t>Сканирование уязвимостей, скрипты реагирования, скрипты для сбора логов; таблица 2, строка 31</t>
         </is>
       </c>
     </row>
     <row r="146" ht="64" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>T-DBE021AA</t>
+          <t>T-78A918BC</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Написание скриптов автоматического реагирования (Python, Bash)</t>
+          <t>Настройка MFA, реализация доступа по ролям /чтение/запись/временный</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Написание скриптов автоматического реагирования (Python, Bash)</t>
+          <t>Настройка MFA, реализация доступа по ролям /чтение/запись/временный</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -6751,34 +6455,34 @@
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Написание скриптов автоматического реагирования (Python, Bash) (1 час лекции).</t>
+          <t>Тема 4. Настройка MFA, реализация доступа по ролям /чтение/запись/временный (5 часов практические занятия).</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Сканирование уязвимостей, скрипты реагирования, скрипты для сбора логов; таблица 2, строка 30</t>
+          <t>Управление доступом и аутентификация; таблица 2, строка 25</t>
         </is>
       </c>
     </row>
     <row r="147" ht="64" customHeight="1">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>T-E5761E9C</t>
+          <t>T-C263D4D0</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>Написание скриптов для сбора и анализа логов (Python)</t>
+          <t>Национальная система обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>АКБ</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>Написание скриптов для сбора и анализа логов (Python)</t>
+          <t>Национальная система обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -6788,34 +6492,34 @@
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Написание скриптов для сбора и анализа логов (Python) (2 часа лекции).</t>
+          <t>Тема 2. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>Сканирование уязвимостей, скрипты реагирования, скрипты для сбора логов; таблица 2, строка 31</t>
+          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
     <row r="148" ht="64" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>T-78A918BC</t>
+          <t>T-C263D4D0</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Настройка MFA, реализация доступа по ролям /чтение/запись/временный</t>
+          <t>Национальная система обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Настройка MFA, реализация доступа по ролям /чтение/запись/временный</t>
+          <t>Национальная система обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -6825,12 +6529,12 @@
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Настройка MFA, реализация доступа по ролям /чтение/запись/временный (5 часов практические занятия).</t>
+          <t>Тема 2. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Управление доступом и аутентификация; таблица 2, строка 26</t>
+          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6551,7 @@
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>АКБ</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
@@ -6862,7 +6566,7 @@
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 2. Национальная система обеспечения кибербезопасности (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G149" s="9" t="inlineStr">
@@ -6884,7 +6588,7 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>ЗИКС</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
@@ -6899,12 +6603,13 @@
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 2. Национальная система обеспечения кибербезопасности 
+(2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
+          <t>Законодательство в области обеспечения кибербезопасности.; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6626,7 @@
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>ЗИОЗ</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
@@ -6936,7 +6641,7 @@
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Национальная система обеспечения кибербезопасности (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 2. Национальная система обеспечения кибербезопасности (3 часа лекции, 1 час тематическая дискуссия).</t>
         </is>
       </c>
       <c r="G151" s="9" t="inlineStr">
@@ -6958,7 +6663,7 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>ЗИКС</t>
+          <t>КВОИ</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
@@ -6972,88 +6677,88 @@
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>Тема 2. Национальная система обеспечения кибербезопасности (4 часа лекции).</t>
+        </is>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="64" customHeight="1">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>T-C263D4D0</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>Национальная система обеспечения кибербезопасности</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>ККС</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>Национальная система обеспечения кибербезопасности</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>Точное соответствие</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Тема 3. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="64" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>T-C263D4D0</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>Национальная система обеспечения кибербезопасности</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>КО</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>Национальная система обеспечения кибербезопасности</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>Точное соответствие</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="inlineStr">
         <is>
           <t>Тема 2. Национальная система обеспечения кибербезопасности 
 (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
-      <c r="G152" s="8" t="inlineStr">
-        <is>
-          <t>Законодательство в области обеспечения кибербезопасности.; таблица 2, строка 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="64" customHeight="1">
-      <c r="A153" s="9" t="inlineStr">
-        <is>
-          <t>T-C263D4D0</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="inlineStr">
-        <is>
-          <t>Национальная система обеспечения кибербезопасности</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>ЗИОЗ</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>Национальная система обеспечения кибербезопасности</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="inlineStr">
-        <is>
-          <t>Точное соответствие</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr">
-        <is>
-          <t>Тема 2. Национальная система обеспечения кибербезопасности (3 часа лекции, 1 час тематическая дискуссия).</t>
-        </is>
-      </c>
-      <c r="G153" s="9" t="inlineStr">
-        <is>
-          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="64" customHeight="1">
-      <c r="A154" s="8" t="inlineStr">
-        <is>
-          <t>T-C263D4D0</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="inlineStr">
-        <is>
-          <t>Национальная система обеспечения кибербезопасности</t>
-        </is>
-      </c>
-      <c r="C154" s="8" t="inlineStr">
-        <is>
-          <t>КВОИ</t>
-        </is>
-      </c>
-      <c r="D154" s="8" t="inlineStr">
-        <is>
-          <t>Национальная система обеспечения кибербезопасности</t>
-        </is>
-      </c>
-      <c r="E154" s="8" t="inlineStr">
-        <is>
-          <t>Точное соответствие</t>
-        </is>
-      </c>
-      <c r="F154" s="8" t="inlineStr">
-        <is>
-          <t>Тема 2. Национальная система обеспечения кибербезопасности (4 часа лекции).</t>
-        </is>
-      </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
+          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности.; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
@@ -7070,7 +6775,7 @@
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
@@ -7085,12 +6790,12 @@
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 2. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 8</t>
+          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
@@ -7107,7 +6812,7 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
@@ -7122,13 +6827,12 @@
       </c>
       <c r="F156" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Национальная система обеспечения кибербезопасности 
-(2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 2. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности.; таблица 2, строка 7</t>
+          <t>Основы обеспечения кибербезопасности; таблица 2, строка 19</t>
         </is>
       </c>
     </row>
@@ -7145,7 +6849,7 @@
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
@@ -7165,29 +6869,29 @@
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
+          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
     <row r="158" ht="64" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>T-C263D4D0</t>
+          <t>T-99A0E09D</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Национальная система обеспечения кибербезопасности</t>
+          <t>Национальная стратегия: экономика данных и цифровое государство (2026–2030)</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Национальная система обеспечения кибербезопасности</t>
+          <t>Национальная стратегия: экономика данных и цифровое государство (2026–2030)</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
@@ -7197,34 +6901,34 @@
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 3. Национальная стратегия: экономика данных и цифровое государство (2026–2030) (2 часа лекции).</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности; таблица 2, строка 19</t>
+          <t>Стратегия государства: экономика данных и цифровое государство (2026–2030); таблица 2, строка 8</t>
         </is>
       </c>
     </row>
     <row r="159" ht="64" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>T-C263D4D0</t>
+          <t>T-9B79997E</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>Национальная система обеспечения кибербезопасности</t>
+          <t>Необходимость и значение киберразведки в обеспечении информационной безопасности</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>Национальная система обеспечения кибербезопасности</t>
+          <t>Необходимость и значение киберразведки в обеспечении информационной безопасности</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
@@ -7234,34 +6938,34 @@
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Национальная система обеспечения кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 5. Необходимость и значение киберразведки в обеспечении информационной безопасности (1 час лекции).</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>Законодательство в области обеспечения кибербезопасности; таблица 2, строка 7</t>
+          <t>Введение в SOAR и TI; таблица 2, строка 38</t>
         </is>
       </c>
     </row>
     <row r="160" ht="64" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>T-99A0E09D</t>
+          <t>T-07538019</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Национальная стратегия: экономика данных и цифровое государство (2026–2030)</t>
+          <t>Нормализация событий, корреляция, обработка ложных событий</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Национальная стратегия: экономика данных и цифровое государство (2026–2030)</t>
+          <t>Нормализация событий, корреляция, обработка ложных событий</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
@@ -7271,34 +6975,34 @@
       </c>
       <c r="F160" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Национальная стратегия: экономика данных и цифровое государство (2026–2030) (2 часа лекции).</t>
+          <t>Тема 5. Нормализация событий, корреляция, обработка ложных событий (1 час практические занятия).</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>Стратегия государства: экономика данных и цифровое государство (2026–2030); таблица 2, строка 8</t>
+          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 31</t>
         </is>
       </c>
     </row>
     <row r="161" ht="64" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>T-9B79997E</t>
+          <t>T-E83E95EB</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>Необходимость и значение киберразведки в обеспечении информационной безопасности</t>
+          <t>«Нулевая бюрократия»: подходы к сокращению административных барьеров</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>Необходимость и значение киберразведки в обеспечении информационной безопасности</t>
+          <t>«Нулевая бюрократия»: подходы к сокращению административных барьеров</t>
         </is>
       </c>
       <c r="E161" s="9" t="inlineStr">
@@ -7308,67 +7012,71 @@
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>Тема 5. Необходимость и значение киберразведки в обеспечении информационной безопасности (1 час лекции).</t>
+          <t>Тема 1. «Нулевая бюрократия»: подходы к сокращению административных барьеров (2 часа лекции).</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>Введение в SOAR и TI; таблица 2, строка 38</t>
+          <t>Нулевая бюрократия и клиентоцентричность; таблица 2, строка 12</t>
         </is>
       </c>
     </row>
     <row r="162" ht="64" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>T-07538019</t>
+          <t>T-89E2CB88</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Нормализация событий, корреляция, обработка ложных событий</t>
+          <t>Обеспечение безопасности информации в информационных системах</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="D162" s="8" t="inlineStr"/>
+          <t>ЗИКС</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>Обеспечение безопасности информации в информационных системах</t>
+        </is>
+      </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Добавлено из программы</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr">
         <is>
-          <t>Тема 5. Нормализация событий, корреляция, обработка ложных событий (1 час практические занятия).</t>
+          <t>Тема 1. Обеспечение безопасности информации в информационных системах (6 часов лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Раздел VI Системы управления информационной безопасностью и событиями безопасности (SIEM).; программа, абзацы 198</t>
+          <t>Обеспечение функционирования системы защиты информации в процессе эксплуатации информационной системы.; таблица 2, строка 14</t>
         </is>
       </c>
     </row>
     <row r="163" ht="64" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>T-E83E95EB</t>
+          <t>T-85A353EA</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>«Нулевая бюрократия»: подходы к сокращению административных барьеров</t>
+          <t>Обеспечение безопасности клиент-серверного соединения</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>«Нулевая бюрократия»: подходы к сокращению административных барьеров</t>
+          <t>Обеспечение безопасности клиент-серверного соединения</t>
         </is>
       </c>
       <c r="E163" s="9" t="inlineStr">
@@ -7378,34 +7086,34 @@
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. «Нулевая бюрократия»: подходы к сокращению административных барьеров (2 часа лекции).</t>
+          <t>Тема 11. Обеспечение безопасности клиент-серверного соединения (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>Нулевая бюрократия и клиентоцентричность; таблица 2, строка 12</t>
+          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 23</t>
         </is>
       </c>
     </row>
     <row r="164" ht="64" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>T-89E2CB88</t>
+          <t>T-25E5D4E2</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Обеспечение безопасности информации в информационных системах</t>
+          <t>Обеспечение безопасности компьютерных сетей</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>ЗИКС</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Обеспечение безопасности информации в информационных системах</t>
+          <t>Обеспечение безопасности компьютерных сетей</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
@@ -7415,34 +7123,34 @@
       </c>
       <c r="F164" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Обеспечение безопасности информации в информационных системах (6 часов лекции, 2 часа круглый стол).</t>
+          <t>Тема 4. Обеспечение безопасности компьютерных сетей (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>Обеспечение функционирования системы защиты информации в процессе эксплуатации информационной системы.; таблица 2, строка 14</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 18</t>
         </is>
       </c>
     </row>
     <row r="165" ht="64" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>T-85A353EA</t>
+          <t>T-25E5D4E2</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>Обеспечение безопасности клиент-серверного соединения</t>
+          <t>Обеспечение безопасности компьютерных сетей</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>ККС</t>
         </is>
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>Обеспечение безопасности клиент-серверного соединения</t>
+          <t>Обеспечение кибербезопасности компьютерных сетей</t>
         </is>
       </c>
       <c r="E165" s="9" t="inlineStr">
@@ -7452,34 +7160,34 @@
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>Тема 11. Обеспечение безопасности клиент-серверного соединения (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 1. Обеспечение кибербезопасности компьютерных сетей (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 23</t>
+          <t>Технические меры по обеспечению кибербезопасности; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="166" ht="64" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>T-25E5D4E2</t>
+          <t>T-02A02E6B</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Обеспечение безопасности компьютерных сетей</t>
+          <t>Обеспечение логирования в системах с контролем доступа. Журналы безопасности OC Windows/Linux</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Обеспечение безопасности компьютерных сетей</t>
+          <t>Обеспечение логирования в системах с контролем доступа. Журналы безопасности OC Windows/Linux</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
@@ -7489,34 +7197,34 @@
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Обеспечение безопасности компьютерных сетей (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 3. Обеспечение логирования в системах с контролем доступа. Журналы безопасности OC Windows/Linux (1 час лекции).</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 18</t>
+          <t>Управление доступом и аутентификация; таблица 2, строка 24</t>
         </is>
       </c>
     </row>
     <row r="167" ht="64" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>T-25E5D4E2</t>
+          <t>T-05A132EB</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>Обеспечение безопасности компьютерных сетей</t>
+          <t>Обзор платформ: R-Vision TI, MISP и др</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>Обеспечение кибербезопасности компьютерных сетей</t>
+          <t>Обзор платформ: R-Vision TI, MISP и др</t>
         </is>
       </c>
       <c r="E167" s="9" t="inlineStr">
@@ -7526,34 +7234,34 @@
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Обеспечение кибербезопасности компьютерных сетей (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 1. Обзор платформ: R-Vision TI, MISP и др. (1 час лекции).</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>Технические меры по обеспечению кибербезопасности; таблица 2, строка 15</t>
+          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 51</t>
         </is>
       </c>
     </row>
     <row r="168" ht="64" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>T-02A02E6B</t>
+          <t>T-D7D89656</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>Обеспечение логирования в системах с контролем доступа. Журналы безопасности OC Windows/Linux</t>
+          <t>Обзор популярных российских SOAR-платформ: R-Vision SOAR, Security Vision SOAR</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Обеспечение логирования в системах с контролем доступа. Журналы безопасности OC Windows/Linux</t>
+          <t>Обзор популярных российских SOAR-платформ: R-Vision SOAR, Security Vision SOAR</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
@@ -7563,34 +7271,34 @@
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Обеспечение логирования в системах с контролем доступа. Журналы безопасности OC Windows/Linux (1 час лекции).</t>
+          <t>Тема 3. Обзор популярных российских SOAR-платформ: R-Vision SOAR, Security Vision SOAR (1 час лекции).</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>Управление доступом и аутентификация; таблица 2, строка 25</t>
+          <t>Введение в SOAR и TI; таблица 2, строка 36</t>
         </is>
       </c>
     </row>
     <row r="169" ht="64" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>T-05A132EB</t>
+          <t>T-6206C2D9</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>Обзор платформ: R-Vision TI, MISP и др</t>
+          <t>Обзор правового регулирования и стандартов в сфере ИИ</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ПТИИМ</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Обзор платформ: R-Vision TI, MISP и др</t>
+          <t>Обзор правового регулирования и стандартов в сфере ИИ</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
@@ -7600,34 +7308,34 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Обзор платформ: R-Vision TI, MISP и др. (1 час лекции).</t>
+          <t>Тема 2. Обзор правового регулирования и стандартов в сфере ИИ (4 часа лекции).</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr">
         <is>
-          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 51</t>
+          <t>Основы ИИ и машинного обучения; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
     <row r="170" ht="64" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>T-D7D89656</t>
+          <t>T-9D2470BA</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>Обзор популярных российских SOAR-платформ: R-Vision SOAR, Security Vision SOAR</t>
+          <t>Обзор требований по обеспечению кибербезопасности различных объектов информационной инфраструктуры</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Обзор популярных российских SOAR-платформ: R-Vision SOAR, Security Vision SOAR</t>
+          <t>Обзор требований по обеспечению кибербезопасности различных объектов информационной инфраструктуры</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
@@ -7637,34 +7345,34 @@
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Обзор популярных российских SOAR-платформ: R-Vision SOAR, Security Vision SOAR (1 час лекции).</t>
+          <t>Тема 2. Обзор требований по обеспечению кибербезопасности различных объектов информационной инфраструктуры (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>Введение в SOAR и TI; таблица 2, строка 36</t>
+          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 14</t>
         </is>
       </c>
     </row>
     <row r="171" ht="64" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>T-6206C2D9</t>
+          <t>T-63831BF0</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>Обзор правового регулирования и стандартов в сфере ИИ</t>
+          <t>Обзор угроз: вредоносы, фишинг, атаки через социальную инженерию</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>ПТИИМ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Обзор правового регулирования и стандартов в сфере ИИ</t>
+          <t>Обзор угроз: вредоносы, фишинг, атаки через социальную инженерию</t>
         </is>
       </c>
       <c r="E171" s="9" t="inlineStr">
@@ -7674,34 +7382,34 @@
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Обзор правового регулирования и стандартов в сфере ИИ (4 часа лекции).</t>
+          <t>Тема 1. Обзор угроз: вредоносы, фишинг, атаки через социальную инженерию (2 часа лекции).</t>
         </is>
       </c>
       <c r="G171" s="9" t="inlineStr">
         <is>
-          <t>Основы ИИ и машинного обучения; таблица 2, строка 7</t>
+          <t>Угрозы информационной безопасности; таблица 2, строка 6</t>
         </is>
       </c>
     </row>
     <row r="172" ht="64" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>T-9D2470BA</t>
+          <t>T-CF0B226D</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>Обзор требований по обеспечению кибербезопасности различных объектов информационной инфраструктуры</t>
+          <t>Обнаружение deepfake</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>ПТИИМ</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Обзор требований по обеспечению кибербезопасности различных объектов информационной инфраструктуры</t>
+          <t>Обнаружение deepfake</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
@@ -7711,34 +7419,34 @@
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Обзор требований по обеспечению кибербезопасности различных объектов информационной инфраструктуры (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 4. Обнаружение deepfake (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 14</t>
+          <t>Практические кейсы применения ИИ в ИБ; таблица 2, строка 21</t>
         </is>
       </c>
     </row>
     <row r="173" ht="64" customHeight="1">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>T-63831BF0</t>
+          <t>T-E8B695F5</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>Обзор угроз: вредоносы, фишинг, атаки через социальную инженерию</t>
+          <t>Обнаружение базовых DGA</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ПТИИМ</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Обзор угроз: вредоносы, фишинг, атаки через социальную инженерию</t>
+          <t>Обнаружение базовых DGA</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
@@ -7748,24 +7456,24 @@
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Обзор угроз: вредоносы, фишинг, атаки через социальную инженерию (2 часа лекции).</t>
+          <t>Тема 3. Обнаружение базовых DGA (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G173" s="9" t="inlineStr">
         <is>
-          <t>Угрозы информационной безопасности; таблица 2, строка 6</t>
+          <t>Практические кейсы применения ИИ в ИБ; таблица 2, строка 20</t>
         </is>
       </c>
     </row>
     <row r="174" ht="64" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>T-CF0B226D</t>
+          <t>T-DB346810</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>Обнаружение deepfake</t>
+          <t>Обнаружение вредоносных файлов</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
@@ -7775,7 +7483,7 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Обнаружение deepfake</t>
+          <t>Обнаружение вредоносных файлов</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
@@ -7785,61 +7493,61 @@
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Обнаружение deepfake (4 часа практические занятия).</t>
+          <t>Тема 2. Обнаружение вредоносных файлов (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>Практические кейсы применения ИИ в ИБ; таблица 2, строка 21</t>
+          <t>Практические кейсы применения ИИ в ИБ; таблица 2, строка 19</t>
         </is>
       </c>
     </row>
     <row r="175" ht="64" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>T-E8B695F5</t>
+          <t>T-A696E34C</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>Обнаружение базовых DGA</t>
+          <t>Обследование и анализ исходных данных на информационную систему</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>ПТИИМ</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>Обнаружение базовых DGA</t>
+          <t>Обследование и анализ исходных данных на информационную систему</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>Точное соответствие</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Обнаружение базовых DGA (4 часа практические занятия).</t>
+          <t>Тема 3. Практикум (8 часов практические занятия).</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>Практические кейсы применения ИИ в ИБ; таблица 2, строка 20</t>
+          <t>Проектирование системы защиты информации организации; таблица 2, строка 12</t>
         </is>
       </c>
     </row>
     <row r="176" ht="64" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>T-DB346810</t>
+          <t>T-E2D6D3F7</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>Обнаружение вредоносных файлов</t>
+          <t>Объяснимый ИИ</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
@@ -7849,7 +7557,7 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Обнаружение вредоносных файлов</t>
+          <t>Объяснимый ИИ</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
@@ -7859,108 +7567,108 @@
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Обнаружение вредоносных файлов (4 часа практические занятия).</t>
+          <t>Тема 3. Объяснимый ИИ (4 часа лекции).</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>Практические кейсы применения ИИ в ИБ; таблица 2, строка 19</t>
+          <t>Алгоритмы, оценка и объяснимость; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
     <row r="177" ht="64" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>T-A696E34C</t>
+          <t>T-6363F810</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>Обследование и анализ исходных данных на информационную систему</t>
+          <t>Определение и функциональная архитектура платформ SOAR</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>Обследование и анализ исходных данных на информационную систему</t>
+          <t>Определение и функциональная архитектура платформ SOAR</t>
         </is>
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
-          <t>Общий практикум</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Практикум (8 часов практические занятия).</t>
+          <t>Тема 1. Определение и функциональная архитектура платформ SOAR (1 час лекции).</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
         <is>
-          <t>Проектирование системы защиты информации организации; таблица 2, строка 12</t>
+          <t>Введение в SOAR и TI; таблица 2, строка 34</t>
         </is>
       </c>
     </row>
     <row r="178" ht="64" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>T-E2D6D3F7</t>
+          <t>T-A152100E</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>Объяснимый ИИ</t>
+          <t>Определение перечня и разработка локальных правовых актов, регламентирующих вопросы защиты информации</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>ПТИИМ</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>Объяснимый ИИ</t>
+          <t>Определение перечня и разработка локальных правовых актов, регламентирующих вопросы защиты информации</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Точное соответствие</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Объяснимый ИИ (4 часа лекции).</t>
+          <t>Тема 9. Практикум (6 часов практические занятия).</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>Алгоритмы, оценка и объяснимость; таблица 2, строка 13</t>
+          <t>Настройка системы защиты информации организации; таблица 2, строка 27</t>
         </is>
       </c>
     </row>
     <row r="179" ht="64" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>T-6363F810</t>
+          <t>T-44810CEF</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>Определение и функциональная архитектура платформ SOAR</t>
+          <t>Оптические сети и технологии xPON</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>Определение и функциональная архитектура платформ SOAR</t>
+          <t>Оптические сети и технологии xPON</t>
         </is>
       </c>
       <c r="E179" s="9" t="inlineStr">
@@ -7970,71 +7678,71 @@
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Определение и функциональная архитектура платформ SOAR (1 час лекции).</t>
+          <t>Тема 3. Оптические сети и технологии xPON (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>Введение в SOAR и TI; таблица 2, строка 34</t>
+          <t>Основы построения компьютерных сетей; таблица 2, строка 8</t>
         </is>
       </c>
     </row>
     <row r="180" ht="64" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>T-A152100E</t>
+          <t>T-D6E9DEFF</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>Определение перечня и разработка локальных правовых актов, регламентирующих вопросы защиты информации</t>
+          <t>Организационные меры по защите информации. Создание и поддержание инфраструктуры защиты информации в организации</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>ККС</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Определение перечня и разработка локальных правовых актов, регламентирующих вопросы защиты информации</t>
+          <t>Организационные меры по защите информации. Создание и поддержание инфраструктуры защиты информации в организации</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Общий практикум</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>Тема 9. Практикум (6 часов практические занятия).</t>
+          <t>Тема 1. Организационные меры по защите информации. Создание и поддержание инфраструктуры защиты информации в организации (6 часов лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>Настройка системы защиты информации организации; таблица 2, строка 27</t>
+          <t>Правовые и организационные меры по обеспечению кибербезопасности; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="181" ht="64" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>T-44810CEF</t>
+          <t>T-150BEB5A</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>Оптические сети и технологии xPON</t>
+          <t>Организация защиты информации в системах электронного документооборота</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>АКБ</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>Оптические сети и технологии xPON</t>
+          <t>Организация защиты информации в системах электронного документооборота</t>
         </is>
       </c>
       <c r="E181" s="9" t="inlineStr">
@@ -8044,34 +7752,34 @@
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Оптические сети и технологии xPON (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 2. Организация защиты информации в системах электронного документооборота (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>Основы построения компьютерных сетей; таблица 2, строка 8</t>
+          <t>Особенности криптографической защиты информации; таблица 2, строка 18</t>
         </is>
       </c>
     </row>
     <row r="182" ht="64" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
         <is>
-          <t>T-D6E9DEFF</t>
+          <t>T-150BEB5A</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>Организационные меры по защите информации. Создание и поддержание инфраструктуры защиты информации в организации</t>
+          <t>Организация защиты информации в системах электронного документооборота</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Организационные меры по защите информации. Создание и поддержание инфраструктуры защиты информации в организации</t>
+          <t>Организация защиты информации в системах электронного документооборота</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
@@ -8081,12 +7789,12 @@
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Организационные меры по защите информации. Создание и поддержание инфраструктуры защиты информации в организации (6 часов лекции, 2 часа круглый стол).</t>
+          <t>Тема 2. Организация защиты информации в системах электронного документооборота (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>Правовые и организационные меры по обеспечению кибербезопасности; таблица 2, строка 10</t>
+          <t>Особенности криптографической защиты информации; таблица 2, строка 26</t>
         </is>
       </c>
     </row>
@@ -8103,7 +7811,7 @@
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>АКБ</t>
+          <t>ЗИКС</t>
         </is>
       </c>
       <c r="D183" s="9" t="inlineStr">
@@ -8123,29 +7831,29 @@
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>Особенности криптографической защиты информации; таблица 2, строка 18</t>
+          <t>Особенности криптографической защиты информации, обрабатываемой в информационных системах.; таблица 2, строка 21</t>
         </is>
       </c>
     </row>
     <row r="184" ht="64" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
         <is>
-          <t>T-150BEB5A</t>
+          <t>T-D12351DD</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>Организация защиты информации в системах электронного документооборота</t>
+          <t>Основные алгоритмы машинного обучения</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>ПТИИМ</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Организация защиты информации в системах электронного документооборота</t>
+          <t>Основные алгоритмы машинного обучения</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
@@ -8155,34 +7863,34 @@
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Организация защиты информации в системах электронного документооборота (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 1. Основные алгоритмы машинного обучения (4 часа лекции).</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>Особенности криптографической защиты информации; таблица 2, строка 26</t>
+          <t>Алгоритмы, оценка и объяснимость; таблица 2, строка 11</t>
         </is>
       </c>
     </row>
     <row r="185" ht="64" customHeight="1">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>T-150BEB5A</t>
+          <t>T-E99406B0</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>Организация защиты информации в системах электронного документооборота</t>
+          <t>Основные аспекты безопасности эксплуатации средств криптографической защиты информации</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>ЗИКС</t>
+          <t>КЗИ</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>Организация защиты информации в системах электронного документооборота</t>
+          <t>Основные аспекты безопасности эксплуатации средств криптографической защиты информации</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
@@ -8192,34 +7900,34 @@
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Организация защиты информации в системах электронного документооборота (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 3. Основные аспекты безопасности эксплуатации средств криптографической защиты информации (4 часа лекции).</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>Особенности криптографической защиты информации, обрабатываемой в информационных системах.; таблица 2, строка 21</t>
+          <t>Средства криптографической защиты информации; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="186" ht="64" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t>T-D12351DD</t>
+          <t>T-8D67A184</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>Основные алгоритмы машинного обучения</t>
+          <t>Основные источники TI (open source, коммерческие, государственные). Стандарты обмена TI: STIX, TAXII</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>ПТИИМ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Основные алгоритмы машинного обучения</t>
+          <t>Основные источники TI (open source, коммерческие, государственные). Стандарты обмена TI: STIX, TAXII</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
@@ -8229,24 +7937,24 @@
       </c>
       <c r="F186" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Основные алгоритмы машинного обучения (4 часа лекции).</t>
+          <t>Тема 7. Основные источники TI (open source, коммерческие, государственные). Стандарты обмена TI: STIX, TAXII (1 час лекции).</t>
         </is>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>Алгоритмы, оценка и объяснимость; таблица 2, строка 11</t>
+          <t>Введение в SOAR и TI; таблица 2, строка 40</t>
         </is>
       </c>
     </row>
     <row r="187" ht="64" customHeight="1">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>T-E99406B0</t>
+          <t>T-1D3B4F15</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>Основные аспекты безопасности эксплуатации средств криптографической защиты информации</t>
+          <t>Основные перспективные направления развития криптографии в Республике Беларусь</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
@@ -8256,7 +7964,7 @@
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>Основные аспекты безопасности эксплуатации средств криптографической защиты информации</t>
+          <t>Основные перспективные направления развития криптографии в Республике Беларусь</t>
         </is>
       </c>
       <c r="E187" s="9" t="inlineStr">
@@ -8266,34 +7974,34 @@
       </c>
       <c r="F187" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Основные аспекты безопасности эксплуатации средств криптографической защиты информации (4 часа лекции).</t>
+          <t>Тема 2. Основные перспективные направления развития криптографии в Республике Беларусь (2 часа лекции).</t>
         </is>
       </c>
       <c r="G187" s="9" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации; таблица 2, строка 15</t>
+          <t>Средства криптографической защиты информации; таблица 2, строка 14</t>
         </is>
       </c>
     </row>
     <row r="188" ht="64" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>T-8D67A184</t>
+          <t>T-9D7A9E2E</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>Основные источники TI (open source, коммерческие, государственные). Стандарты обмена TI: STIX, TAXII</t>
+          <t>Основные принципы и инструменты выявления, анализа действий нарушителя и работы вредоносного программного обеспечения</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Основные источники TI (open source, коммерческие, государственные). Стандарты обмена TI: STIX, TAXII</t>
+          <t>Основные принципы и инструменты выявления, анализа действий нарушителя и работы вредоносного программного обеспечения</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
@@ -8303,34 +8011,34 @@
       </c>
       <c r="F188" s="8" t="inlineStr">
         <is>
-          <t>Тема 7. Основные источники TI (open source, коммерческие, государственные). Стандарты обмена TI: STIX, TAXII (1 час лекции).</t>
+          <t>Тема 2. Основные принципы и инструменты выявления, анализа действий нарушителя и работы вредоносного программного обеспечения (1 час лекции, 3 часа практические занятия).</t>
         </is>
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>Введение в SOAR и TI; таблица 2, строка 40</t>
+          <t>Оценка эффективности защищенности инфраструктуры. Реагирование на киберинциденты; таблица 2, строка 20</t>
         </is>
       </c>
     </row>
     <row r="189" ht="64" customHeight="1">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>T-1D3B4F15</t>
+          <t>T-6FF1CBA0</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>Основные перспективные направления развития криптографии в Республике Беларусь</t>
+          <t>Основные субъекты, участвующие в процессах управления цифровой трансформацией государственного управления</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
         <is>
-          <t>КЗИ</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>Основные перспективные направления развития криптографии в Республике Беларусь</t>
+          <t>Основные субъекты, участвующие в процессах управления цифровой трансформацией государственного управления</t>
         </is>
       </c>
       <c r="E189" s="9" t="inlineStr">
@@ -8340,34 +8048,34 @@
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Основные перспективные направления развития криптографии в Республике Беларусь (2 часа лекции).</t>
+          <t>Тема 2. Основные субъекты, участвующие в процессах управления цифровой трансформацией государственного управления (2 часа лекции).</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации; таблица 2, строка 14</t>
+          <t>Управление цифровой трансформацией: офисы цифровизации; таблица 2, строка 21</t>
         </is>
       </c>
     </row>
     <row r="190" ht="64" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>T-9D7A9E2E</t>
+          <t>T-A0BAE9BD</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>Основные принципы и инструменты выявления, анализа действий нарушителя и работы вредоносного программного обеспечения</t>
+          <t>Основные функции: оркестрация, автоматизация, реагирование</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Основные принципы и инструменты выявления, анализа действий нарушителя и работы вредоносного программного обеспечения</t>
+          <t>Основные функции: оркестрация, автоматизация, реагирование</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
@@ -8377,34 +8085,34 @@
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Основные принципы и инструменты выявления, анализа действий нарушителя и работы вредоносного программного обеспечения (1 час лекции, 3 часа практические занятия).</t>
+          <t>Тема 2. Основные функции: оркестрация, автоматизация, реагирование (1 час лекции).</t>
         </is>
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>Оценка эффективности защищенности инфраструктуры. Реагирование на киберинциденты; таблица 2, строка 21</t>
+          <t>Введение в SOAR и TI; таблица 2, строка 35</t>
         </is>
       </c>
     </row>
     <row r="191" ht="64" customHeight="1">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>T-6FF1CBA0</t>
+          <t>T-104C2C72</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>Основные субъекты, участвующие в процессах управления цифровой трансформацией государственного управления</t>
+          <t>Основы защиты персональных данных. Законодательство о персональных данных</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>Основные субъекты, участвующие в процессах управления цифровой трансформацией государственного управления</t>
+          <t>Основы защиты персональных данных. Законодательство о персональных данных</t>
         </is>
       </c>
       <c r="E191" s="9" t="inlineStr">
@@ -8414,34 +8122,35 @@
       </c>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Основные субъекты, участвующие в процессах управления цифровой трансформацией государственного управления (2 часа лекции).</t>
+          <t>Тема 1. Основы защиты персональных данных. Законодательство 
+о персональных данных (2 часа лекции).</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>Управление цифровой трансформацией: офисы цифровизации; таблица 2, строка 21</t>
+          <t>Основы защиты персональных данных. Законодательство о персональных данных.; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="192" ht="64" customHeight="1">
       <c r="A192" s="8" t="inlineStr">
         <is>
-          <t>T-A0BAE9BD</t>
+          <t>T-F16DF157</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>Основные функции: оркестрация, автоматизация, реагирование</t>
+          <t>Основы информационной безопасности: понятие, цели, принципы. CIA-модель: конфиденциальность, целостность, доступность</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Основные функции: оркестрация, автоматизация, реагирование</t>
+          <t>Основы информационной безопасности: понятие, цели, принципы. CIA-модель: конфиденциальность, целостность, доступность</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
@@ -8451,34 +8160,34 @@
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Основные функции: оркестрация, автоматизация, реагирование (1 час лекции).</t>
+          <t>Тема 1. Основы информационной безопасности: понятие, цели, принципы. CIA-модель: конфиденциальность, целостность, доступность (3 часа лекции).</t>
         </is>
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>Введение в SOAR и TI; таблица 2, строка 35</t>
+          <t>Введение в кибербезопасность; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="193" ht="64" customHeight="1">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>T-104C2C72</t>
+          <t>T-16947C9D</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>Основы защиты персональных данных. Законодательство о персональных данных</t>
+          <t>Основы политик информационной безопасности и системы управления информационной безопасности</t>
         </is>
       </c>
       <c r="C193" s="9" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>Основы защиты персональных данных. Законодательство о персональных данных</t>
+          <t>Основы политик информационной безопасности и системы управления информационной безопасности</t>
         </is>
       </c>
       <c r="E193" s="9" t="inlineStr">
@@ -8488,35 +8197,34 @@
       </c>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Основы защиты персональных данных. Законодательство 
-о персональных данных (2 часа лекции).</t>
+          <t>Тема 2. Основы политик информационной безопасности и системы управления информационной безопасности (1 час лекции).</t>
         </is>
       </c>
       <c r="G193" s="9" t="inlineStr">
         <is>
-          <t>Основы защиты персональных данных. Законодательство о персональных данных.; таблица 2, строка 9</t>
+          <t>Управление информационной безопасностью; таблица 2, строка 12</t>
         </is>
       </c>
     </row>
     <row r="194" ht="64" customHeight="1">
       <c r="A194" s="8" t="inlineStr">
         <is>
-          <t>T-F16DF157</t>
+          <t>T-BE30B5FB</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>Основы информационной безопасности: понятие, цели, принципы. CIA-модель: конфиденциальность, целостность, доступность</t>
+          <t>Особенности подтверждения соответствия средств защиты информации в Национальной системе подтверждения соответствия</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Основы информационной безопасности: понятие, цели, принципы. CIA-модель: конфиденциальность, целостность, доступность</t>
+          <t>Особенности подтверждения соответствия средств защиты информации в Национальной системе подтверждения соответствия</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
@@ -8526,34 +8234,34 @@
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Основы информационной безопасности: понятие, цели, принципы. CIA-модель: конфиденциальность, целостность, доступность (3 часа лекции).</t>
+          <t>Тема 1. Особенности подтверждения соответствия средств защиты информации в Национальной системе подтверждения соответствия (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t>Введение в кибербезопасность; таблица 2, строка 10</t>
+          <t>Подтверждение соответствия средств защиты информации; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="195" ht="64" customHeight="1">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>T-16947C9D</t>
+          <t>T-DBE83A65</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>Основы политик информационной безопасности и системы управления информационной безопасности</t>
+          <t>Особенности эксплуатации системы защиты информации организации</t>
         </is>
       </c>
       <c r="C195" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>Основы политик информационной безопасности и системы управления информационной безопасности</t>
+          <t>Особенности эксплуатации системы защиты информации организации</t>
         </is>
       </c>
       <c r="E195" s="9" t="inlineStr">
@@ -8563,34 +8271,34 @@
       </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Основы политик информационной безопасности и системы управления информационной безопасности (1 час лекции).</t>
+          <t>Тема 1. Особенности эксплуатации системы защиты информации организации (4 часа лекции).</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>Управление информационной безопасностью; таблица 2, строка 12</t>
+          <t>Особенности эксплуатации системы защиты информации организации; таблица 2, строка 34</t>
         </is>
       </c>
     </row>
     <row r="196" ht="64" customHeight="1">
       <c r="A196" s="8" t="inlineStr">
         <is>
-          <t>T-BE30B5FB</t>
+          <t>T-70E46FD9</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>Особенности подтверждения соответствия средств защиты информации в Национальной системе подтверждения соответствия</t>
+          <t>Офисы цифровизации: функции, роли, взаимодействие</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Особенности подтверждения соответствия средств защиты информации в Национальной системе подтверждения соответствия</t>
+          <t>Офисы цифровизации: функции, роли, взаимодействие</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
@@ -8600,34 +8308,34 @@
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Особенности подтверждения соответствия средств защиты информации в Национальной системе подтверждения соответствия (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 3. Офисы цифровизации: функции, роли, взаимодействие (2 часа лекции).</t>
         </is>
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>Подтверждение соответствия средств защиты информации; таблица 2, строка 9</t>
+          <t>Управление цифровой трансформацией: офисы цифровизации; таблица 2, строка 20</t>
         </is>
       </c>
     </row>
     <row r="197" ht="64" customHeight="1">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>T-DBE83A65</t>
+          <t>T-98153B1D</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>Особенности эксплуатации системы защиты информации организации</t>
+          <t>Планирование и проведение аудита кибербезопасности. Управление процессом аудита</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>Особенности эксплуатации системы защиты информации организации</t>
+          <t>Планирование и проведение аудита кибербезопасности. Управление процессом аудита</t>
         </is>
       </c>
       <c r="E197" s="9" t="inlineStr">
@@ -8637,24 +8345,24 @@
       </c>
       <c r="F197" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Особенности эксплуатации системы защиты информации организации (4 часа лекции).</t>
+          <t>Тема 3. Планирование и проведение аудита кибербезопасности. Управление процессом аудита (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>Особенности эксплуатации системы защиты информации организации; таблица 2, строка 34</t>
+          <t>Аудит кибербезопасности; таблица 2, строка 21</t>
         </is>
       </c>
     </row>
     <row r="198" ht="64" customHeight="1">
       <c r="A198" s="8" t="inlineStr">
         <is>
-          <t>T-70E46FD9</t>
+          <t>T-1A3B7311</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>Офисы цифровизации: функции, роли, взаимодействие</t>
+          <t>Платформенная модель «Цифровое государство»: архитектура и компоненты</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
@@ -8664,7 +8372,7 @@
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Офисы цифровизации: функции, роли, взаимодействие</t>
+          <t>Платформенная модель «Цифровое государство»: архитектура и компоненты</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
@@ -8674,67 +8382,71 @@
       </c>
       <c r="F198" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Офисы цифровизации: функции, роли, взаимодействие (2 часа лекции).</t>
+          <t>Тема 4. Платформенная модель «Цифровое государство»: архитектура и компоненты (2 часа лекции).</t>
         </is>
       </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t>Управление цифровой трансформацией: офисы цифровизации; таблица 2, строка 20</t>
+          <t>Стратегия государства: экономика данных и цифровое государство (2026–2030); таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="199" ht="64" customHeight="1">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>T-9CDE7CD7</t>
+          <t>T-ED6B85B9</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>Оценка эффективности защищенности. Оценка степени зрелости компании, оценка правильности назначения ответственных лиц на предприятии и выстроенных бизнес-процессов. Аудит информационной безопасности и ее составляющие. Тесты на проникновение</t>
+          <t>Плейбук в системе SOAR: понятие, структура и принципы построения</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>Оценка эффективности защищенности. Оценка степени зрелости компании, оценка правильности назначения ответственных лиц на предприятии и выстроенных бизнес-процессов. Аудит информационной безопасности и ее составляющие. Тесты на проникновение</t>
+          <t>Плейбук в системе SOAR: понятие, структура и принципы построения</t>
         </is>
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>Описание не найдено</t>
-        </is>
-      </c>
-      <c r="F199" s="9" t="inlineStr"/>
+          <t>Точное соответствие</t>
+        </is>
+      </c>
+      <c r="F199" s="9" t="inlineStr">
+        <is>
+          <t>Тема 4. Плейбук в системе SOAR: понятие, структура и принципы построения (1 час лекции).</t>
+        </is>
+      </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
-          <t>Оценка эффективности защищенности инфраструктуры. Реагирование на киберинциденты; таблица 2, строка 19</t>
+          <t>Интеграция и использование SOAR в ЦКБ; таблица 2, строка 46</t>
         </is>
       </c>
     </row>
     <row r="200" ht="64" customHeight="1">
       <c r="A200" s="8" t="inlineStr">
         <is>
-          <t>T-98153B1D</t>
+          <t>T-DEAC0563</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>Планирование и проведение аудита кибербезопасности. Управление процессом аудита</t>
+          <t>Поведенческие триггеры</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Планирование и проведение аудита кибербезопасности. Управление процессом аудита</t>
+          <t>Поведенческие триггеры</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
@@ -8744,61 +8456,61 @@
       </c>
       <c r="F200" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Планирование и проведение аудита кибербезопасности. Управление процессом аудита (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 4. Поведенческие триггеры (1 час лекции).</t>
         </is>
       </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t>Аудит кибербезопасности; таблица 2, строка 21</t>
+          <t>Автоматизация обработки инцидентов; таблица 2, строка 62</t>
         </is>
       </c>
     </row>
     <row r="201" ht="64" customHeight="1">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>T-1A3B7311</t>
+          <t>T-073C7E19</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>Платформенная модель «Цифровое государство»: архитектура и компоненты</t>
+          <t>Подготовка исходных данных к проведению аттестации системы защиты информации</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>Платформенная модель «Цифровое государство»: архитектура и компоненты</t>
+          <t>Подготовка исходных данных к проведению аттестации системы защиты информации</t>
         </is>
       </c>
       <c r="E201" s="9" t="inlineStr">
         <is>
-          <t>Точное соответствие</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="F201" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Платформенная модель «Цифровое государство»: архитектура и компоненты (2 часа лекции).</t>
+          <t>Тема 9. Практикум (6 часов практические занятия).</t>
         </is>
       </c>
       <c r="G201" s="9" t="inlineStr">
         <is>
-          <t>Стратегия государства: экономика данных и цифровое государство (2026–2030); таблица 2, строка 9</t>
+          <t>Настройка системы защиты информации организации; таблица 2, строка 28</t>
         </is>
       </c>
     </row>
     <row r="202" ht="64" customHeight="1">
       <c r="A202" s="8" t="inlineStr">
         <is>
-          <t>T-ED6B85B9</t>
+          <t>T-17154455</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>Плейбук в системе SOAR: понятие, структура и принципы построения</t>
+          <t>Подключение внешних фидов, загрузка собственных индикаторов</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
@@ -8808,7 +8520,7 @@
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Плейбук в системе SOAR: понятие, структура и принципы построения</t>
+          <t>Подключение внешних фидов, загрузка собственных индикаторов</t>
         </is>
       </c>
       <c r="E202" s="8" t="inlineStr">
@@ -8818,34 +8530,34 @@
       </c>
       <c r="F202" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Плейбук в системе SOAR: понятие, структура и принципы построения (1 час лекции).</t>
+          <t>Тема 2. Подключение внешних фидов, загрузка собственных индикаторов (1 час лекции).</t>
         </is>
       </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t>Интеграция и использование SOAR в ЦКБ; таблица 2, строка 46</t>
+          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 52</t>
         </is>
       </c>
     </row>
     <row r="203" ht="64" customHeight="1">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>T-DEAC0563</t>
+          <t>T-A7207ADC</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>Поведенческие триггеры</t>
+          <t>Подключение различных источников событий</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>Поведенческие триггеры</t>
+          <t>Подключение различных источников событий</t>
         </is>
       </c>
       <c r="E203" s="9" t="inlineStr">
@@ -8855,61 +8567,61 @@
       </c>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Поведенческие триггеры (1 час лекции).</t>
+          <t>Тема 4. Подключение различных источников событий (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G203" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация обработки инцидентов; таблица 2, строка 62</t>
+          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 30</t>
         </is>
       </c>
     </row>
     <row r="204" ht="64" customHeight="1">
       <c r="A204" s="8" t="inlineStr">
         <is>
-          <t>T-073C7E19</t>
+          <t>T-8C6E913A</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>Подготовка исходных данных к проведению аттестации системы защиты информации</t>
+          <t>Подсистемы безопасности операционных систем</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>ЗИКС</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Подготовка исходных данных к проведению аттестации системы защиты информации</t>
+          <t>Подсистемы безопасности операционных систем</t>
         </is>
       </c>
       <c r="E204" s="8" t="inlineStr">
         <is>
-          <t>Общий практикум</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F204" s="8" t="inlineStr">
         <is>
-          <t>Тема 9. Практикум (6 часов практические занятия).</t>
+          <t>Тема 4. Подсистемы безопасности операционных систем (4 часа лекции, 4 часа круглый стол).</t>
         </is>
       </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t>Настройка системы защиты информации организации; таблица 2, строка 28</t>
+          <t>Обеспечение функционирования системы защиты информации в процессе эксплуатации информационной системы.; таблица 2, строка 17</t>
         </is>
       </c>
     </row>
     <row r="205" ht="64" customHeight="1">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>T-17154455</t>
+          <t>T-8A655C52</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>Подключение внешних фидов, загрузка собственных индикаторов</t>
+          <t>Поиск и сбор доказательств в изолированной среде</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
@@ -8919,7 +8631,7 @@
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>Подключение внешних фидов, загрузка собственных индикаторов</t>
+          <t>Поиск и сбор доказательств в изолированной среде</t>
         </is>
       </c>
       <c r="E205" s="9" t="inlineStr">
@@ -8929,104 +8641,108 @@
       </c>
       <c r="F205" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Подключение внешних фидов, загрузка собственных индикаторов (1 час лекции).</t>
+          <t>Тема 7. Поиск и сбор доказательств в изолированной среде (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G205" s="9" t="inlineStr">
         <is>
-          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 52</t>
+          <t>Введение в киберкриминалистику; таблица 2, строка 27</t>
         </is>
       </c>
     </row>
     <row r="206" ht="64" customHeight="1">
       <c r="A206" s="8" t="inlineStr">
         <is>
-          <t>T-FC0E5E98</t>
+          <t>T-7209DCF1</t>
         </is>
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>Подключение источника, нормализация событий, корреляция, обработка ложных событий</t>
+          <t>Понятие аудита кибербезопасности, цели и задачи его проведения. Актуальность аудита, основные принципы и виды аудита кибербезопасности</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Подключение источника, нормализация событий, корреляция, обработка ложных событий</t>
+          <t>Понятие аудита кибербезопасности, цели и задачи его проведения. Актуальность аудита, основные принципы и виды аудита кибербезопасности</t>
         </is>
       </c>
       <c r="E206" s="8" t="inlineStr">
         <is>
-          <t>Сопоставление фрагментов</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F206" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Подключение различных источников событий (2 часа практические занятия). / Тема 5. Нормализация событий, корреляция, обработка ложных событий (1 час практические занятия).</t>
+          <t>Тема 1. Понятие аудита кибербезопасности, цели и задачи его проведения. Актуальность аудита, основные принципы и виды аудита кибербезопасности (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 33</t>
+          <t>Аудит кибербезопасности; таблица 2, строка 19</t>
         </is>
       </c>
     </row>
     <row r="207" ht="64" customHeight="1">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>T-A7207ADC</t>
+          <t>T-6261BCD8</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>Подключение различных источников событий</t>
+          <t>Понятие пилотного проекта в сфере цифрового развития</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="D207" s="9" t="inlineStr"/>
+          <t>ЦТГУ</t>
+        </is>
+      </c>
+      <c r="D207" s="9" t="inlineStr">
+        <is>
+          <t>Понятие пилотного проекта в сфере цифрового развития</t>
+        </is>
+      </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>Добавлено из программы</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F207" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Подключение различных источников событий (2 часа практические занятия).</t>
+          <t>Тема 1. Понятие пилотного проекта в сфере цифрового развития (2 часа лекции).</t>
         </is>
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
-          <t>Раздел VI Системы управления информационной безопасностью и событиями безопасности (SIEM).; программа, абзацы 196</t>
+          <t>Пилотный проект в сфере цифрового развития как способ реализации цифровой трансформации государственного управления; таблица 2, строка 24</t>
         </is>
       </c>
     </row>
     <row r="208" ht="64" customHeight="1">
       <c r="A208" s="8" t="inlineStr">
         <is>
-          <t>T-8C6E913A</t>
+          <t>T-D16425D5</t>
         </is>
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>Подсистемы безопасности операционных систем</t>
+          <t>Порядок регистрации КИ. Порядок взаимодействия центра кибербезопасности с национальным центром кибербезопасности</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>ЗИКС</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Подсистемы безопасности операционных систем</t>
+          <t>Порядок регистрации КИ. Порядок взаимодействия центра кибербезопасности с национальным центром кибербезопасности</t>
         </is>
       </c>
       <c r="E208" s="8" t="inlineStr">
@@ -9036,24 +8752,24 @@
       </c>
       <c r="F208" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Подсистемы безопасности операционных систем (4 часа лекции, 4 часа круглый стол).</t>
+          <t>Тема 6. Порядок регистрации КИ. Порядок взаимодействия центра кибербезопасности с национальным центром кибербезопасности (1 час лекции).</t>
         </is>
       </c>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t>Обеспечение функционирования системы защиты информации в процессе эксплуатации информационной системы.; таблица 2, строка 17</t>
+          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 32</t>
         </is>
       </c>
     </row>
     <row r="209" ht="64" customHeight="1">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>T-8A655C52</t>
+          <t>T-162738D1</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>Поиск и сбор доказательств в изолированной среде</t>
+          <t>Построение матрицы рисков и разработка политики безопасности</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
@@ -9063,7 +8779,7 @@
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>Поиск и сбор доказательств в изолированной среде</t>
+          <t>Построение матрицы рисков и разработка политики безопасности</t>
         </is>
       </c>
       <c r="E209" s="9" t="inlineStr">
@@ -9073,34 +8789,34 @@
       </c>
       <c r="F209" s="9" t="inlineStr">
         <is>
-          <t>Тема 7. Поиск и сбор доказательств в изолированной среде (2 часа практические занятия).</t>
+          <t>Тема 3. Построение матрицы рисков и разработка политики безопасности (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G209" s="9" t="inlineStr">
         <is>
-          <t>Введение в киберкриминалистику; таблица 2, строка 27</t>
+          <t>Управление информационной безопасностью; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
     <row r="210" ht="64" customHeight="1">
       <c r="A210" s="8" t="inlineStr">
         <is>
-          <t>T-7209DCF1</t>
+          <t>T-BE634D39</t>
         </is>
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>Понятие аудита кибербезопасности, цели и задачи его проведения. Актуальность аудита, основные принципы и виды аудита кибербезопасности</t>
+          <t>Практические аспекты аттестации систем защиты информации</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>АКБ</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Понятие аудита кибербезопасности, цели и задачи его проведения. Актуальность аудита, основные принципы и виды аудита кибербезопасности</t>
+          <t>Практические аспекты аттестации систем защиты информации</t>
         </is>
       </c>
       <c r="E210" s="8" t="inlineStr">
@@ -9110,34 +8826,34 @@
       </c>
       <c r="F210" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Понятие аудита кибербезопасности, цели и задачи его проведения. Актуальность аудита, основные принципы и виды аудита кибербезопасности (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 4. Практические аспекты аттестации систем защиты информации (1 час лекции, 3 часа практические занятия).</t>
         </is>
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>Аудит кибербезопасности; таблица 2, строка 19</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="211" ht="64" customHeight="1">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>T-6261BCD8</t>
+          <t>T-BE634D39</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>Понятие пилотного проекта в сфере цифрового развития</t>
+          <t>Практические аспекты аттестации систем защиты информации</t>
         </is>
       </c>
       <c r="C211" s="9" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>Понятие пилотного проекта в сфере цифрового развития</t>
+          <t>Практические аспекты аттестации систем защиты информации</t>
         </is>
       </c>
       <c r="E211" s="9" t="inlineStr">
@@ -9147,34 +8863,34 @@
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Понятие пилотного проекта в сфере цифрового развития (2 часа лекции).</t>
+          <t>Тема 5. Практические аспекты аттестации систем защиты информации (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>Пилотный проект в сфере цифрового развития как способ реализации цифровой трансформации государственного управления; таблица 2, строка 24</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
     <row r="212" ht="64" customHeight="1">
       <c r="A212" s="8" t="inlineStr">
         <is>
-          <t>T-D16425D5</t>
+          <t>T-4F3C56FD</t>
         </is>
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>Порядок регистрации КИ. Порядок взаимодействия центра кибербезопасности с национальным центром кибербезопасности</t>
+          <t>Презентация и защита проектного решения</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Порядок регистрации КИ. Порядок взаимодействия центра кибербезопасности с национальным центром кибербезопасности</t>
+          <t>Презентация и защита проектного решения</t>
         </is>
       </c>
       <c r="E212" s="8" t="inlineStr">
@@ -9184,34 +8900,34 @@
       </c>
       <c r="F212" s="8" t="inlineStr">
         <is>
-          <t>Тема 6. Порядок регистрации КИ. Порядок взаимодействия центра кибербезопасности с национальным центром кибербезопасности (1 час лекции).</t>
+          <t>Тема 2. Презентация и защита проектного решения (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
-          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 32</t>
+          <t>Практический блок; таблица 2, строка 28</t>
         </is>
       </c>
     </row>
     <row r="213" ht="64" customHeight="1">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>T-162738D1</t>
+          <t>T-8CD6AA88</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>Построение матрицы рисков и разработка политики безопасности</t>
+          <t>Прикладные протоколы. DHCP. DNS. HTTP. SMTP. HTTPS. Установка и настройка серверов для работы по прикладным протоколам</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>Построение матрицы рисков и разработка политики безопасности</t>
+          <t>Прикладные протоколы. DHCP. DNS. HTTP. SMTP. HTTPS. Установка и настройка серверов для работы по прикладным протоколам</t>
         </is>
       </c>
       <c r="E213" s="9" t="inlineStr">
@@ -9221,34 +8937,34 @@
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Построение матрицы рисков и разработка политики безопасности (2 часа практические занятия).</t>
+          <t>Тема 6. Прикладные протоколы. DHCP. DNS. HTTP. SMTP. HTTPS. Установка и настройка серверов для работы по прикладным протоколам (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G213" s="9" t="inlineStr">
         <is>
-          <t>Управление информационной безопасностью; таблица 2, строка 13</t>
+          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 18</t>
         </is>
       </c>
     </row>
     <row r="214" ht="64" customHeight="1">
       <c r="A214" s="8" t="inlineStr">
         <is>
-          <t>T-BE634D39</t>
+          <t>T-6DC0F613</t>
         </is>
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты аттестации систем защиты информации</t>
+          <t>Прикладные протоколы. Описание и применение прикладных протоколов</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>АКБ</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты аттестации систем защиты информации</t>
+          <t>Прикладные протоколы. Описание и применение прикладных протоколов</t>
         </is>
       </c>
       <c r="E214" s="8" t="inlineStr">
@@ -9258,34 +8974,34 @@
       </c>
       <c r="F214" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Практические аспекты аттестации систем защиты информации (1 час лекции, 3 часа практические занятия).</t>
+          <t>Тема 5. Прикладные протоколы. Описание и применение прикладных протоколов (2 часа лекции).</t>
         </is>
       </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 15</t>
+          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 17</t>
         </is>
       </c>
     </row>
     <row r="215" ht="64" customHeight="1">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>T-BE634D39</t>
+          <t>T-77482F27</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты аттестации систем защиты информации</t>
+          <t>Применение командной строки</t>
         </is>
       </c>
       <c r="C215" s="9" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты аттестации систем защиты информации</t>
+          <t>Применение командной строки</t>
         </is>
       </c>
       <c r="E215" s="9" t="inlineStr">
@@ -9295,34 +9011,34 @@
       </c>
       <c r="F215" s="9" t="inlineStr">
         <is>
-          <t>Тема 5. Практические аспекты аттестации систем защиты информации (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 9. Применение командной строки (4 часа практических занятий).</t>
         </is>
       </c>
       <c r="G215" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 13</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 23</t>
         </is>
       </c>
     </row>
     <row r="216" ht="64" customHeight="1">
       <c r="A216" s="8" t="inlineStr">
         <is>
-          <t>T-4F3C56FD</t>
+          <t>T-A7827890</t>
         </is>
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>Презентация и защита проектного решения</t>
+          <t>Применение машинного обучения в ИБ</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>ПТИИМ</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Презентация и защита проектного решения</t>
+          <t>Применение машинного обучения в ИБ</t>
         </is>
       </c>
       <c r="E216" s="8" t="inlineStr">
@@ -9332,34 +9048,34 @@
       </c>
       <c r="F216" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Презентация и защита проектного решения (4 часа практические занятия).</t>
+          <t>Тема 1. Применение машинного обучения в ИБ (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G216" s="8" t="inlineStr">
         <is>
-          <t>Практический блок; таблица 2, строка 28</t>
+          <t>Применение ИИ в ИБ; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="217" ht="64" customHeight="1">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>T-8CD6AA88</t>
+          <t>T-A91970F7</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>Прикладные протоколы. DHCP. DNS. HTTP. SMTP. HTTPS. Установка и настройка серверов для работы по прикладным протоколам</t>
+          <t>Принципы работы и защиты NGFW</t>
         </is>
       </c>
       <c r="C217" s="9" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>Прикладные протоколы. DHCP. DNS. HTTP. SMTP. HTTPS. Установка и настройка серверов для работы по прикладным протоколам</t>
+          <t>Принципы работы и защиты NGFW</t>
         </is>
       </c>
       <c r="E217" s="9" t="inlineStr">
@@ -9369,71 +9085,71 @@
       </c>
       <c r="F217" s="9" t="inlineStr">
         <is>
-          <t>Тема 6. Прикладные протоколы. DHCP. DNS. HTTP. SMTP. HTTPS. Установка и настройка серверов для работы по прикладным протоколам (4 часа практические занятия).</t>
+          <t>Тема 3. Принципы работы и защиты NGFW (1 час лекции).</t>
         </is>
       </c>
       <c r="G217" s="9" t="inlineStr">
         <is>
-          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 18</t>
+          <t>Сбор данных и предотвращение атак; таблица 2, строка 17</t>
         </is>
       </c>
     </row>
     <row r="218" ht="64" customHeight="1">
       <c r="A218" s="8" t="inlineStr">
         <is>
-          <t>T-6DC0F613</t>
+          <t>T-AD42D9C6</t>
         </is>
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>Прикладные протоколы. Описание и применение прикладных протоколов</t>
+          <t>Проведение оценки рисков кибербезопасности</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Прикладные протоколы. Описание и применение прикладных протоколов</t>
+          <t>Проведение оценки рисков кибербезопасности</t>
         </is>
       </c>
       <c r="E218" s="8" t="inlineStr">
         <is>
-          <t>Точное соответствие</t>
+          <t>Название отличается</t>
         </is>
       </c>
       <c r="F218" s="8" t="inlineStr">
         <is>
-          <t>Тема 5. Прикладные протоколы. Описание и применение прикладных протоколов (2 часа лекции).</t>
+          <t>Тема 3. Проведение оценки рисков кибербезопасности в организации (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G218" s="8" t="inlineStr">
         <is>
-          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 17</t>
+          <t>Управление рисками кибербезопасности; таблица 2, строка 17</t>
         </is>
       </c>
     </row>
     <row r="219" ht="64" customHeight="1">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>T-77482F27</t>
+          <t>T-8E4770CC</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>Применение командной строки</t>
+          <t>Проверка утечек, анализ IP и доменов, поиск в даркнете</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>Применение командной строки</t>
+          <t>Проверка утечек, анализ IP и доменов, поиск в даркнете</t>
         </is>
       </c>
       <c r="E219" s="9" t="inlineStr">
@@ -9443,34 +9159,34 @@
       </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>Тема 9. Применение командной строки (4 часа практических занятий).</t>
+          <t>Тема 6. Проверка утечек, анализ IP и доменов, поиск в даркнете (1 час лекции).</t>
         </is>
       </c>
       <c r="G219" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 23</t>
+          <t>Введение в киберкриминалистику; таблица 2, строка 26</t>
         </is>
       </c>
     </row>
     <row r="220" ht="64" customHeight="1">
       <c r="A220" s="8" t="inlineStr">
         <is>
-          <t>T-A7827890</t>
+          <t>T-8BF890EA</t>
         </is>
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>Применение машинного обучения в ИБ</t>
+          <t>Программно-аппаратные методы фильтрации трафика</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>ПТИИМ</t>
+          <t>ККС</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Применение машинного обучения в ИБ</t>
+          <t>Программно-аппаратные методы фильтрации трафика</t>
         </is>
       </c>
       <c r="E220" s="8" t="inlineStr">
@@ -9480,34 +9196,34 @@
       </c>
       <c r="F220" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Применение машинного обучения в ИБ (4 часа практические занятия).</t>
+          <t>Тема 8. Программно-аппаратные методы фильтрации трафика (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G220" s="8" t="inlineStr">
         <is>
-          <t>Применение ИИ в ИБ; таблица 2, строка 15</t>
+          <t>Технические меры по обеспечению кибербезопасности; таблица 2, строка 22</t>
         </is>
       </c>
     </row>
     <row r="221" ht="64" customHeight="1">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>T-A91970F7</t>
+          <t>T-8BF890EA</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>Принципы работы и защиты NGFW</t>
+          <t>Программно-аппаратные методы фильтрации трафика</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>Принципы работы и защиты NGFW</t>
+          <t>Программно-аппаратные методы фильтрации трафика</t>
         </is>
       </c>
       <c r="E221" s="9" t="inlineStr">
@@ -9517,71 +9233,71 @@
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Принципы работы и защиты NGFW (1 час лекции).</t>
+          <t>Тема 9. Программно-аппаратные методы фильтрации трафика (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>Сбор данных и предотвращение атак; таблица 2, строка 17</t>
+          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 21</t>
         </is>
       </c>
     </row>
     <row r="222" ht="64" customHeight="1">
       <c r="A222" s="8" t="inlineStr">
         <is>
-          <t>T-AD42D9C6</t>
+          <t>T-94624995</t>
         </is>
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>Проведение оценки рисков кибербезопасности</t>
+          <t>Проектирование и внедрение структурированных кабельных систем</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Проведение оценки рисков кибербезопасности</t>
+          <t>Проектирование и внедрение структурированных кабельных систем</t>
         </is>
       </c>
       <c r="E222" s="8" t="inlineStr">
         <is>
-          <t>Название отличается</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F222" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Проведение оценки рисков кибербезопасности в организации (4 часа практические занятия).</t>
+          <t>Тема 1. Проектирование и внедрение структурированных кабельных систем (2 часа лекции).</t>
         </is>
       </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности; таблица 2, строка 17</t>
+          <t>Основы построения компьютерных сетей; таблица 2, строка 6</t>
         </is>
       </c>
     </row>
     <row r="223" ht="64" customHeight="1">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>T-8E4770CC</t>
+          <t>T-F4D2B23F</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>Проверка утечек, анализ IP и доменов, поиск в даркнете</t>
+          <t>Проектирование и создание систем защиты информации</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>Проверка утечек, анализ IP и доменов, поиск в даркнете</t>
+          <t>Проектирование и создание систем защиты информации</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
@@ -9591,34 +9307,34 @@
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>Тема 6. Проверка утечек, анализ IP и доменов, поиск в даркнете (1 час лекции).</t>
+          <t>Тема 3. Проектирование и создание систем защиты информации (4 часа лекции).</t>
         </is>
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>Введение в киберкриминалистику; таблица 2, строка 26</t>
+          <t>Настройка системы защиты информации организации; таблица 2, строка 19</t>
         </is>
       </c>
     </row>
     <row r="224" ht="64" customHeight="1">
       <c r="A224" s="8" t="inlineStr">
         <is>
-          <t>T-8BF890EA</t>
+          <t>T-9BFE2CB8</t>
         </is>
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>Программно-аппаратные методы фильтрации трафика</t>
+          <t>Проектный подход в цифровых инициативах</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Программно-аппаратные методы фильтрации трафика</t>
+          <t>Проектный подход в цифровых инициативах</t>
         </is>
       </c>
       <c r="E224" s="8" t="inlineStr">
@@ -9628,24 +9344,24 @@
       </c>
       <c r="F224" s="8" t="inlineStr">
         <is>
-          <t>Тема 8. Программно-аппаратные методы фильтрации трафика (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 4. Проектный подход в цифровых инициативах (2 часа лекции).</t>
         </is>
       </c>
       <c r="G224" s="8" t="inlineStr">
         <is>
-          <t>Технические меры по обеспечению кибербезопасности; таблица 2, строка 22</t>
+          <t>Управление цифровой трансформацией: офисы цифровизации; таблица 2, строка 22</t>
         </is>
       </c>
     </row>
     <row r="225" ht="64" customHeight="1">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>T-8BF890EA</t>
+          <t>T-DE1BDCB4</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>Программно-аппаратные методы фильтрации трафика</t>
+          <t>Противодействие целенаправленным кибератакам</t>
         </is>
       </c>
       <c r="C225" s="9" t="inlineStr">
@@ -9655,7 +9371,7 @@
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>Программно-аппаратные методы фильтрации трафика</t>
+          <t>Противодействие целенаправленным кибератакам</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
@@ -9665,34 +9381,34 @@
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>Тема 9. Программно-аппаратные методы фильтрации трафика (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 2. Противодействие целенаправленным кибератакам (8 часов лекции, 2 часа практические занятия, 6 часов лабораторные занятия).</t>
         </is>
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 21</t>
+          <t>Методологические основы обеспечения кибербезопасности корпоративных систем; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="226" ht="64" customHeight="1">
       <c r="A226" s="8" t="inlineStr">
         <is>
-          <t>T-94624995</t>
+          <t>T-9550B70A</t>
         </is>
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>Проектирование и внедрение структурированных кабельных систем</t>
+          <t>Протоколы DHCPv4, DHCPv6</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Проектирование и внедрение структурированных кабельных систем</t>
+          <t>Протоколы DHCPv4, DHCPv6</t>
         </is>
       </c>
       <c r="E226" s="8" t="inlineStr">
@@ -9702,34 +9418,34 @@
       </c>
       <c r="F226" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Проектирование и внедрение структурированных кабельных систем (2 часа лекции).</t>
+          <t>Тема 4. Протоколы DHCPv4, DHCPv6 (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G226" s="8" t="inlineStr">
         <is>
-          <t>Основы построения компьютерных сетей; таблица 2, строка 6</t>
+          <t>Маршрутизация. IPv4 и IPv6 адресация; таблица 2, строка 18</t>
         </is>
       </c>
     </row>
     <row r="227" ht="64" customHeight="1">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>T-F4D2B23F</t>
+          <t>T-E0A32CD6</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>Проектирование и создание систем защиты информации</t>
+          <t>Работа с false positive: фильтрация, обогащение, подтверждение</t>
         </is>
       </c>
       <c r="C227" s="9" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>Проектирование и создание систем защиты информации</t>
+          <t>Работа с false positive: фильтрация, обогащение, подтверждение</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
@@ -9739,34 +9455,34 @@
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Проектирование и создание систем защиты информации (4 часа лекции).</t>
+          <t>Тема 6. Работа с false positive: фильтрация, обогащение, подтверждение (1 час лекции).</t>
         </is>
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>Настройка системы защиты информации организации; таблица 2, строка 19</t>
+          <t>Автоматизация обработки инцидентов; таблица 2, строка 64</t>
         </is>
       </c>
     </row>
     <row r="228" ht="64" customHeight="1">
       <c r="A228" s="8" t="inlineStr">
         <is>
-          <t>T-9BFE2CB8</t>
+          <t>T-7615F8DC</t>
         </is>
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>Проектный подход в цифровых инициативах</t>
+          <t>Разбор типичных инцидентов</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Проектный подход в цифровых инициативах</t>
+          <t>Разбор типичных инцидентов</t>
         </is>
       </c>
       <c r="E228" s="8" t="inlineStr">
@@ -9776,34 +9492,34 @@
       </c>
       <c r="F228" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Проектный подход в цифровых инициативах (2 часа лекции).</t>
+          <t>Тема 4. Разбор типичных инцидентов (3 часа практические занятия).</t>
         </is>
       </c>
       <c r="G228" s="8" t="inlineStr">
         <is>
-          <t>Управление цифровой трансформацией: офисы цифровизации; таблица 2, строка 22</t>
+          <t>Угрозы информационной безопасности; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="229" ht="64" customHeight="1">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>T-DE1BDCB4</t>
+          <t>T-F21D19B1</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>Противодействие целенаправленным кибератакам</t>
+          <t>Разработка и документирование политик информационной безопасности</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>ККС</t>
         </is>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>Противодействие целенаправленным кибератакам</t>
+          <t>Разработка и документирование политик информационной безопасности</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
@@ -9813,71 +9529,71 @@
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Противодействие целенаправленным кибератакам (8 часов лекции, 2 часа практические занятия, 6 часов лабораторные занятия).</t>
+          <t>Тема 3. Разработка и документирование политик информационной безопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности корпоративных систем; таблица 2, строка 10</t>
+          <t>Правовые и организационные меры по обеспечению кибербезопасности; таблица 2, строка 12</t>
         </is>
       </c>
     </row>
     <row r="230" ht="64" customHeight="1">
       <c r="A230" s="8" t="inlineStr">
         <is>
-          <t>T-9550B70A</t>
+          <t>T-44695169</t>
         </is>
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>Протоколы DHCPv4, DHCPv6</t>
+          <t>Разработка политики информационной безопасности</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Протоколы DHCPv4, DHCPv6</t>
+          <t>Разработка политики информационной безопасности</t>
         </is>
       </c>
       <c r="E230" s="8" t="inlineStr">
         <is>
-          <t>Точное соответствие</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="F230" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Протоколы DHCPv4, DHCPv6 (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 3. Практикум (8 часов практические занятия).</t>
         </is>
       </c>
       <c r="G230" s="8" t="inlineStr">
         <is>
-          <t>Маршрутизация. IPv4 и IPv6 адресация; таблица 2, строка 18</t>
+          <t>Проектирование системы защиты информации организации; таблица 2, строка 14</t>
         </is>
       </c>
     </row>
     <row r="231" ht="64" customHeight="1">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>T-E0A32CD6</t>
+          <t>T-356EA386</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>Работа с false positive: фильтрация, обогащение, подтверждение</t>
+          <t>Разработка предложений (проектных решений) по цифровой трансформации</t>
         </is>
       </c>
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>Работа с false positive: фильтрация, обогащение, подтверждение</t>
+          <t>Разработка предложений (проектных решений) по цифровой трансформации</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
@@ -9887,98 +9603,98 @@
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>Тема 6. Работа с false positive: фильтрация, обогащение, подтверждение (1 час лекции).</t>
+          <t>Тема 1. Разработка предложений (проектных решений) по цифровой трансформации (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация обработки инцидентов; таблица 2, строка 64</t>
+          <t>Практический блок; таблица 2, строка 27</t>
         </is>
       </c>
     </row>
     <row r="232" ht="64" customHeight="1">
       <c r="A232" s="8" t="inlineStr">
         <is>
-          <t>T-7615F8DC</t>
+          <t>T-FEC6B01F</t>
         </is>
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>Разбор типичных инцидентов</t>
+          <t>Разработка программы и методики аттестации</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Разбор типичных инцидентов</t>
+          <t>Разработка программы и методики аттестации</t>
         </is>
       </c>
       <c r="E232" s="8" t="inlineStr">
         <is>
-          <t>Точное соответствие</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="F232" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Разбор типичных инцидентов (3 часа практические занятия).</t>
+          <t>Тема 1. Практикум (6 часов практические занятия).</t>
         </is>
       </c>
       <c r="G232" s="8" t="inlineStr">
         <is>
-          <t>Угрозы информационной безопасности; таблица 2, строка 9</t>
+          <t>Аттестация системы защиты информации организации; таблица 2, строка 31</t>
         </is>
       </c>
     </row>
     <row r="233" ht="64" customHeight="1">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>T-F21D19B1</t>
+          <t>T-6AE9A30B</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>Разработка и документирование политик информационной безопасности</t>
+          <t>Разработка структурной и логической схем системы защиты информации</t>
         </is>
       </c>
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Разработка и документирование политик информационной безопасности</t>
+          <t>Разработка структурной и логической схем системы защиты информации</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>Точное соответствие</t>
+          <t>Общий практикум</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Разработка и документирование политик информационной безопасности (4 часа лекции).</t>
+          <t>Тема 9. Практикум (6 часов практические занятия).</t>
         </is>
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>Правовые и организационные меры по обеспечению кибербезопасности; таблица 2, строка 12</t>
+          <t>Настройка системы защиты информации организации; таблица 2, строка 26</t>
         </is>
       </c>
     </row>
     <row r="234" ht="64" customHeight="1">
       <c r="A234" s="8" t="inlineStr">
         <is>
-          <t>T-44695169</t>
+          <t>T-26DD464B</t>
         </is>
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>Разработка политики информационной безопасности</t>
+          <t>Разработка технического задания на создание системы защиты информации</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
@@ -9988,7 +9704,7 @@
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Разработка политики информационной безопасности</t>
+          <t>Разработка технического задания на создание системы защиты информации</t>
         </is>
       </c>
       <c r="E234" s="8" t="inlineStr">
@@ -10003,29 +9719,29 @@
       </c>
       <c r="G234" s="8" t="inlineStr">
         <is>
-          <t>Проектирование системы защиты информации организации; таблица 2, строка 14</t>
+          <t>Проектирование системы защиты информации организации; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="235" ht="64" customHeight="1">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>T-356EA386</t>
+          <t>T-02668D31</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>Разработка предложений (проектных решений) по цифровой трансформации</t>
+          <t>Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний</t>
         </is>
       </c>
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>ЗИОЗ</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>Разработка предложений (проектных решений) по цифровой трансформации</t>
+          <t>Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
@@ -10035,61 +9751,61 @@
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Разработка предложений (проектных решений) по цифровой трансформации (2 часа практические занятия).</t>
+          <t>Тема 2. Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G235" s="9" t="inlineStr">
         <is>
-          <t>Практический блок; таблица 2, строка 27</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 14</t>
         </is>
       </c>
     </row>
     <row r="236" ht="64" customHeight="1">
       <c r="A236" s="8" t="inlineStr">
         <is>
-          <t>T-FEC6B01F</t>
+          <t>T-02668D31</t>
         </is>
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>Разработка программы и методики аттестации</t>
+          <t>Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>ТЗПД</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>Разработка программы и методики аттестации</t>
+          <t>Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний</t>
         </is>
       </c>
       <c r="E236" s="8" t="inlineStr">
         <is>
-          <t>Общий практикум</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F236" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Практикум (6 часов практические занятия).</t>
+          <t>Тема 4. Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний (4 часа практические занятия).</t>
         </is>
       </c>
       <c r="G236" s="8" t="inlineStr">
         <is>
-          <t>Аттестация системы защиты информации организации; таблица 2, строка 31</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 17</t>
         </is>
       </c>
     </row>
     <row r="237" ht="64" customHeight="1">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>T-6AE9A30B</t>
+          <t>T-6ED2200F</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>Разработка структурной и логической схем системы защиты информации</t>
+          <t>Разработка технического отчета и протокола испытаний</t>
         </is>
       </c>
       <c r="C237" s="9" t="inlineStr">
@@ -10099,7 +9815,7 @@
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>Разработка структурной и логической схем системы защиты информации</t>
+          <t>Разработка технического отчета и протокола испытаний</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
@@ -10109,61 +9825,61 @@
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>Тема 9. Практикум (6 часов практические занятия).</t>
+          <t>Тема 1. Практикум (6 часов практические занятия).</t>
         </is>
       </c>
       <c r="G237" s="9" t="inlineStr">
         <is>
-          <t>Настройка системы защиты информации организации; таблица 2, строка 26</t>
+          <t>Аттестация системы защиты информации организации; таблица 2, строка 32</t>
         </is>
       </c>
     </row>
     <row r="238" ht="64" customHeight="1">
       <c r="A238" s="8" t="inlineStr">
         <is>
-          <t>T-26DD464B</t>
+          <t>T-EA89BB86</t>
         </is>
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>Разработка технического задания на создание системы защиты информации</t>
+          <t>Реагирование на киберинциденты</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>Разработка технического задания на создание системы защиты информации</t>
+          <t>Реагирование на киберинциденты</t>
         </is>
       </c>
       <c r="E238" s="8" t="inlineStr">
         <is>
-          <t>Общий практикум</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F238" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Практикум (8 часов практические занятия).</t>
+          <t>Тема 3. Реагирование на киберинциденты (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G238" s="8" t="inlineStr">
         <is>
-          <t>Проектирование системы защиты информации организации; таблица 2, строка 15</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 17</t>
         </is>
       </c>
     </row>
     <row r="239" ht="64" customHeight="1">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>T-02668D31</t>
+          <t>T-EA89BB86</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний</t>
+          <t>Реагирование на киберинциденты</t>
         </is>
       </c>
       <c r="C239" s="9" t="inlineStr">
@@ -10173,7 +9889,7 @@
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний</t>
+          <t>Реагирование на киберинциденты</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
@@ -10183,34 +9899,34 @@
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний (4 часа практические занятия).</t>
+          <t>Тема 4. Реагирование на киберинциденты (3 часа лекции, 1 час тематическая дискуссия).</t>
         </is>
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 14</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 16</t>
         </is>
       </c>
     </row>
     <row r="240" ht="64" customHeight="1">
       <c r="A240" s="8" t="inlineStr">
         <is>
-          <t>T-02668D31</t>
+          <t>T-EA89BB86</t>
         </is>
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний</t>
+          <t>Реагирование на киберинциденты</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>ТЗПД</t>
+          <t>КВОИ</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний</t>
+          <t>Реагирование на киберинциденты</t>
         </is>
       </c>
       <c r="E240" s="8" t="inlineStr">
@@ -10220,71 +9936,71 @@
       </c>
       <c r="F240" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Разработка технического задания, программы и методики испытаний, технического отчета и протокола испытаний (4 часа практические занятия).</t>
+          <t>Тема 6. Реагирование на киберинциденты (2 часа лекции).</t>
         </is>
       </c>
       <c r="G240" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 17</t>
+          <t>Практические аспекты обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 18</t>
         </is>
       </c>
     </row>
     <row r="241" ht="64" customHeight="1">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>T-6ED2200F</t>
+          <t>T-BEC1F534</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>Разработка технического отчета и протокола испытаний</t>
+          <t>Реагирование на киберинциденты. Подготовительные, организационные и практические мероприятия</t>
         </is>
       </c>
       <c r="C241" s="9" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>Разработка технического отчета и протокола испытаний</t>
+          <t>Реагирование на киберинциденты. Подготовительные, организационные и практические мероприятия</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>Общий практикум</t>
+          <t>Название отличается</t>
         </is>
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Практикум (6 часов практические занятия).</t>
+          <t>Тема 1. Реагирование на КИ. Подготовительные, организационные и практические мероприятия (1 час лекции, 3 часа практические занятия).</t>
         </is>
       </c>
       <c r="G241" s="9" t="inlineStr">
         <is>
-          <t>Аттестация системы защиты информации организации; таблица 2, строка 32</t>
+          <t>Оценка эффективности защищенности инфраструктуры. Реагирование на киберинциденты; таблица 2, строка 19</t>
         </is>
       </c>
     </row>
     <row r="242" ht="64" customHeight="1">
       <c r="A242" s="8" t="inlineStr">
         <is>
-          <t>T-EA89BB86</t>
+          <t>T-78C3BD08</t>
         </is>
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>Реагирование на киберинциденты</t>
+          <t>Роли и взаимодействие команд (ЦКБ, IR)</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>Реагирование на киберинциденты</t>
+          <t>Роли и взаимодействие команд (ЦКБ, IR)</t>
         </is>
       </c>
       <c r="E242" s="8" t="inlineStr">
@@ -10294,34 +10010,34 @@
       </c>
       <c r="F242" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Реагирование на киберинциденты (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 3. Роли и взаимодействие команд (ЦКБ, IR) (1 час лекции).</t>
         </is>
       </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 17</t>
+          <t>Автоматизация обработки инцидентов; таблица 2, строка 61</t>
         </is>
       </c>
     </row>
     <row r="243" ht="64" customHeight="1">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>T-EA89BB86</t>
+          <t>T-074D07AA</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>Реагирование на киберинциденты</t>
+          <t>Роли и обязанности в ЦКБ</t>
         </is>
       </c>
       <c r="C243" s="9" t="inlineStr">
         <is>
-          <t>ЗИОЗ</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Реагирование на киберинциденты</t>
+          <t>Роли и обязанности в ЦКБ</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
@@ -10331,34 +10047,34 @@
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Реагирование на киберинциденты (3 часа лекции, 1 час тематическая дискуссия).</t>
+          <t>Тема 2. Роли и обязанности в ЦКБ (1 час лекции).</t>
         </is>
       </c>
       <c r="G243" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 16</t>
+          <t>Основные функции центров обеспечения кибербезопасности и реагирования на киберинциденты объектов информационной инфраструктуры государственных органов и иных организаций (ЦКБ), процессы информационной безопасности; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="244" ht="64" customHeight="1">
       <c r="A244" s="8" t="inlineStr">
         <is>
-          <t>T-EA89BB86</t>
+          <t>T-97CE9DB3</t>
         </is>
       </c>
       <c r="B244" s="8" t="inlineStr">
         <is>
-          <t>Реагирование на киберинциденты</t>
+          <t>Роль SOAR в структуре ЦКБ и его взаимодействие с системами SIEM</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>КВОИ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>Реагирование на киберинциденты</t>
+          <t>Роль SOAR в структуре ЦКБ и его взаимодействие с системами SIEM</t>
         </is>
       </c>
       <c r="E244" s="8" t="inlineStr">
@@ -10368,71 +10084,71 @@
       </c>
       <c r="F244" s="8" t="inlineStr">
         <is>
-          <t>Тема 6. Реагирование на киберинциденты (2 часа лекции).</t>
+          <t>Тема 4. Роль SOAR в структуре ЦКБ и его взаимодействие с системами SIEM (1 час лекции).</t>
         </is>
       </c>
       <c r="G244" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 18</t>
+          <t>Введение в SOAR и TI; таблица 2, строка 37</t>
         </is>
       </c>
     </row>
     <row r="245" ht="64" customHeight="1">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>T-BEC1F534</t>
+          <t>T-15C7B62E</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>Реагирование на киберинциденты. Подготовительные, организационные и практические мероприятия</t>
+          <t>Роль и задачи администратора кибербезопасности</t>
         </is>
       </c>
       <c r="C245" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>АКБ</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Реагирование на киберинциденты. Подготовительные, организационные и практические мероприятия</t>
+          <t>Роль и задачи администратора кибербезопасности</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>Название отличается</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Реагирование на КИ. Подготовительные, организационные и практические мероприятия (1 час лекции, 3 часа практические занятия).</t>
+          <t>Тема 1. Роль и задачи администратора кибербезопасности (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G245" s="9" t="inlineStr">
         <is>
-          <t>Оценка эффективности защищенности инфраструктуры. Реагирование на киберинциденты; таблица 2, строка 20</t>
+          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="246" ht="64" customHeight="1">
       <c r="A246" s="8" t="inlineStr">
         <is>
-          <t>T-78C3BD08</t>
+          <t>T-0BCE0FDD</t>
         </is>
       </c>
       <c r="B246" s="8" t="inlineStr">
         <is>
-          <t>Роли и взаимодействие команд (ЦКБ, IR)</t>
+          <t>Роль и задачи кибербезопасности</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Роли и взаимодействие команд (ЦКБ, IR)</t>
+          <t>Роль и задачи кибербезопасности</t>
         </is>
       </c>
       <c r="E246" s="8" t="inlineStr">
@@ -10442,34 +10158,34 @@
       </c>
       <c r="F246" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Роли и взаимодействие команд (ЦКБ, IR) (1 час лекции).</t>
+          <t>Тема 1. Роль и задачи кибербезопасности (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G246" s="8" t="inlineStr">
         <is>
-          <t>Автоматизация обработки инцидентов; таблица 2, строка 61</t>
+          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 11</t>
         </is>
       </c>
     </row>
     <row r="247" ht="64" customHeight="1">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>T-074D07AA</t>
+          <t>T-62D4D00A</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
         <is>
-          <t>Роли и обязанности в ЦКБ</t>
+          <t>Роль и задачи обеспечения кибербезопасности в сфере здравоохранения. Объекты информационной инфраструктуры организаций здравоохранения</t>
         </is>
       </c>
       <c r="C247" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ЗИОЗ</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Роли и обязанности в ЦКБ</t>
+          <t>Роль и задачи обеспечения кибербезопасности в сфере здравоохранения. Объекты информационной инфраструктуры организаций здравоохранения</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
@@ -10479,24 +10195,24 @@
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Роли и обязанности в ЦКБ (1 час лекции).</t>
+          <t>Тема 1. Роль и задачи обеспечения кибербезопасности в сфере здравоохранения. Объекты информационной инфраструктуры организаций здравоохранения (3 часа лекции, 1 час тематическая дискуссия).</t>
         </is>
       </c>
       <c r="G247" s="9" t="inlineStr">
         <is>
-          <t>Основные функции центров обеспечения кибербезопасности и реагирования на киберинциденты объектов информационной инфраструктуры государственных органов и иных организаций (ЦКБ), процессы информационной безопасности; таблица 2, строка 15</t>
+          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="248" ht="64" customHeight="1">
       <c r="A248" s="8" t="inlineStr">
         <is>
-          <t>T-97CE9DB3</t>
+          <t>T-FE107062</t>
         </is>
       </c>
       <c r="B248" s="8" t="inlineStr">
         <is>
-          <t>Роль SOAR в структуре ЦКБ и его взаимодействие с системами SIEM</t>
+          <t>Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
@@ -10506,7 +10222,7 @@
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Роль SOAR в структуре ЦКБ и его взаимодействие с системами SIEM</t>
+          <t>Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования</t>
         </is>
       </c>
       <c r="E248" s="8" t="inlineStr">
@@ -10516,34 +10232,34 @@
       </c>
       <c r="F248" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Роль SOAR в структуре ЦКБ и его взаимодействие с системами SIEM (1 час лекции).</t>
+          <t>Тема 7. Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>Введение в SOAR и TI; таблица 2, строка 37</t>
+          <t>Интеграция и использование SOAR в ЦКБ; таблица 2, строка 49</t>
         </is>
       </c>
     </row>
     <row r="249" ht="64" customHeight="1">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>T-15C7B62E</t>
+          <t>T-FE107062</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
         <is>
-          <t>Роль и задачи администратора кибербезопасности</t>
+          <t>Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования</t>
         </is>
       </c>
       <c r="C249" s="9" t="inlineStr">
         <is>
-          <t>АКБ</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Роль и задачи администратора кибербезопасности</t>
+          <t>Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
@@ -10553,34 +10269,34 @@
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Роль и задачи администратора кибербезопасности (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 1. Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования (3 часа практические занятия).</t>
         </is>
       </c>
       <c r="G249" s="9" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 9</t>
+          <t>Отработка практических заданий на базе киберполигона; таблица 2, строка 43</t>
         </is>
       </c>
     </row>
     <row r="250" ht="64" customHeight="1">
       <c r="A250" s="8" t="inlineStr">
         <is>
-          <t>T-0BCE0FDD</t>
+          <t>T-236E36A0</t>
         </is>
       </c>
       <c r="B250" s="8" t="inlineStr">
         <is>
-          <t>Роль и задачи кибербезопасности</t>
+          <t>Сводки, категории, IOC и контекст</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Роль и задачи кибербезопасности</t>
+          <t>Сводки, категории, IOC и контекст</t>
         </is>
       </c>
       <c r="E250" s="8" t="inlineStr">
@@ -10590,34 +10306,34 @@
       </c>
       <c r="F250" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Роль и задачи кибербезопасности (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 3. Сводки, категории, IOC и контекст (1 час лекции).</t>
         </is>
       </c>
       <c r="G250" s="8" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 11</t>
+          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 53</t>
         </is>
       </c>
     </row>
     <row r="251" ht="64" customHeight="1">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>T-62D4D00A</t>
+          <t>T-F041B9F5</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
         <is>
-          <t>Роль и задачи обеспечения кибербезопасности в сфере здравоохранения. Объекты информационной инфраструктуры организаций здравоохранения</t>
+          <t>Связка TI + SOAR: автоматическое обогащение</t>
         </is>
       </c>
       <c r="C251" s="9" t="inlineStr">
         <is>
-          <t>ЗИОЗ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Роль и задачи обеспечения кибербезопасности в сфере здравоохранения. Объекты информационной инфраструктуры организаций здравоохранения</t>
+          <t>Связка TI + SOAR: автоматическое обогащение</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
@@ -10627,71 +10343,71 @@
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Роль и задачи обеспечения кибербезопасности в сфере здравоохранения. Объекты информационной инфраструктуры организаций здравоохранения (3 часа лекции, 1 час тематическая дискуссия).</t>
+          <t>Тема 4. Связка TI + SOAR: автоматическое обогащение (1 час лекции).</t>
         </is>
       </c>
       <c r="G251" s="9" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 9</t>
+          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 54</t>
         </is>
       </c>
     </row>
     <row r="252" ht="64" customHeight="1">
       <c r="A252" s="8" t="inlineStr">
         <is>
-          <t>T-FE107062</t>
+          <t>T-F331D245</t>
         </is>
       </c>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t>Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования</t>
+          <t>Сегментация сети и виртуальные локальные сети (VLAN)</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Базовая конфигурация SOAR: написания плейбука, отработка плейбука, процесс автоматизации</t>
+          <t>Сегментация сети и виртуальные локальные сети (VLAN)</t>
         </is>
       </c>
       <c r="E252" s="8" t="inlineStr">
         <is>
-          <t>Название отличается</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F252" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования (3 часа практические занятия).</t>
+          <t>Тема 4. Сегментация сети и виртуальные локальные сети (VLAN) (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G252" s="8" t="inlineStr">
         <is>
-          <t>Отработка практических заданий на базе киберполигона; таблица 2, строка 44</t>
+          <t>Основы построения компьютерных сетей; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="253" ht="64" customHeight="1">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>T-FE107062</t>
+          <t>T-1EF20152</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
         <is>
-          <t>Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования</t>
+          <t>Сетевая (IP) адресация и маршрутизация</t>
         </is>
       </c>
       <c r="C253" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования</t>
+          <t>Сетевая (IP) адресация и маршрутизация</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
@@ -10701,24 +10417,24 @@
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Тема 7. Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования (2 часа практические занятия).</t>
+          <t>Тема 6. Сетевая (IP) адресация и маршрутизация (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G253" s="9" t="inlineStr">
         <is>
-          <t>Интеграция и использование SOAR в ЦКБ; таблица 2, строка 49</t>
+          <t>Основы построения компьютерных сетей; таблица 2, строка 11</t>
         </is>
       </c>
     </row>
     <row r="254" ht="64" customHeight="1">
       <c r="A254" s="8" t="inlineStr">
         <is>
-          <t>T-236E36A0</t>
+          <t>T-9654B8BE</t>
         </is>
       </c>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>Сводки, категории, IOC и контекст</t>
+          <t>Симуляция фишинговой атаки: обнаружение (SIEM), обогащение IOC (TI), реакция (SOAR)</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
@@ -10728,7 +10444,7 @@
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Сводки, категории, IOC и контекст</t>
+          <t>Симуляция фишинговой атаки: обнаружение (SIEM), обогащение IOC (TI), реакция (SOAR)</t>
         </is>
       </c>
       <c r="E254" s="8" t="inlineStr">
@@ -10738,34 +10454,34 @@
       </c>
       <c r="F254" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Сводки, категории, IOC и контекст (1 час лекции).</t>
+          <t>Тема 4. Симуляция фишинговой атаки: обнаружение (SIEM), обогащение IOC (TI), реакция (SOAR) (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G254" s="8" t="inlineStr">
         <is>
-          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 53</t>
+          <t>Связь SOAR/TI/SIEM; таблица 2, строка 70</t>
         </is>
       </c>
     </row>
     <row r="255" ht="64" customHeight="1">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>T-F041B9F5</t>
+          <t>T-B989A854</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>Связка TI + SOAR: автоматическое обогащение</t>
+          <t>Система информационной безопасности критически важного объекта информатизации</t>
         </is>
       </c>
       <c r="C255" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>КВОИ</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Связка TI + SOAR: автоматическое обогащение</t>
+          <t>Система информационной безопасности критически важного объекта информатизации</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
@@ -10775,34 +10491,34 @@
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Связка TI + SOAR: автоматическое обогащение (1 час лекции).</t>
+          <t>Тема 3. Система информационной безопасности критически важного объекта информатизации (9 часов лекции, 3 часа тематическая дискуссия).</t>
         </is>
       </c>
       <c r="G255" s="9" t="inlineStr">
         <is>
-          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 54</t>
+          <t>Практические аспекты обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="256" ht="64" customHeight="1">
       <c r="A256" s="8" t="inlineStr">
         <is>
-          <t>T-F331D245</t>
+          <t>T-B15220B1</t>
         </is>
       </c>
       <c r="B256" s="8" t="inlineStr">
         <is>
-          <t>Сегментация сети и виртуальные локальные сети (VLAN)</t>
+          <t>Система менеджмента информационной безопасности</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>КВОИ</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>Сегментация сети и виртуальные локальные сети (VLAN)</t>
+          <t>Система менеджмента информационной безопасности</t>
         </is>
       </c>
       <c r="E256" s="8" t="inlineStr">
@@ -10812,34 +10528,34 @@
       </c>
       <c r="F256" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Сегментация сети и виртуальные локальные сети (VLAN) (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 1. Система менеджмента информационной безопасности (3 часа лекции, 1 час тематическая дискуссия).</t>
         </is>
       </c>
       <c r="G256" s="8" t="inlineStr">
         <is>
-          <t>Основы построения компьютерных сетей; таблица 2, строка 9</t>
+          <t>Методологические основы обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="257" ht="64" customHeight="1">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>T-1EF20152</t>
+          <t>T-5FC18368</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>Сетевая (IP) адресация и маршрутизация</t>
+          <t>Системы сбора событий информационной безопасности</t>
         </is>
       </c>
       <c r="C257" s="9" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Сетевая (IP) адресация и маршрутизация</t>
+          <t>Системы сбора событий информационной безопасности</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
@@ -10849,34 +10565,34 @@
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>Тема 6. Сетевая (IP) адресация и маршрутизация (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 8. Системы сбора событий информационной безопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G257" s="9" t="inlineStr">
         <is>
-          <t>Основы построения компьютерных сетей; таблица 2, строка 11</t>
+          <t>Настройка системы защиты информации организации; таблица 2, строка 24</t>
         </is>
       </c>
     </row>
     <row r="258" ht="64" customHeight="1">
       <c r="A258" s="8" t="inlineStr">
         <is>
-          <t>T-9654B8BE</t>
+          <t>T-C32FEFB2</t>
         </is>
       </c>
       <c r="B258" s="8" t="inlineStr">
         <is>
-          <t>Симуляция фишинговой атаки: обнаружение (SIEM), обогащение IOC (TI), реакция (SOAR)</t>
+          <t>Совместное использование протоколов IPv4 и IPv6</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>Симуляция фишинговой атаки: обнаружение (SIEM), обогащение IOC (TI), реакция (SOAR)</t>
+          <t>Совместное использование протоколов IPv4 и IPv6</t>
         </is>
       </c>
       <c r="E258" s="8" t="inlineStr">
@@ -10886,34 +10602,34 @@
       </c>
       <c r="F258" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Симуляция фишинговой атаки: обнаружение (SIEM), обогащение IOC (TI), реакция (SOAR) (2 часа практические занятия).</t>
+          <t>Тема 2. Совместное использование протоколов IPv4 и IPv6 (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G258" s="8" t="inlineStr">
         <is>
-          <t>Связь SOAR/TI/SIEM; таблица 2, строка 70</t>
+          <t>Маршрутизация. IPv4 и IPv6 адресация; таблица 2, строка 16</t>
         </is>
       </c>
     </row>
     <row r="259" ht="64" customHeight="1">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>T-B989A854</t>
+          <t>T-78EF094E</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
         <is>
-          <t>Система информационной безопасности критически важного объекта информатизации</t>
+          <t>Совместное функционирование систем SIEM, SOAR и TIP</t>
         </is>
       </c>
       <c r="C259" s="9" t="inlineStr">
         <is>
-          <t>КВОИ</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Система информационной безопасности критически важного объекта информатизации</t>
+          <t>Совместное функционирование систем SIEM, SOAR, и TIP</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
@@ -10923,34 +10639,34 @@
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Система информационной безопасности критически важного объекта информатизации (9 часов лекции, 3 часа тематическая дискуссия).</t>
+          <t>Тема 3. Совместное функционирование систем SIEM, SOAR и TIP (2 часа лекции).</t>
         </is>
       </c>
       <c r="G259" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 15</t>
+          <t>SOAR, TIP - Автоматизация реагирования; таблица 2, строка 36</t>
         </is>
       </c>
     </row>
     <row r="260" ht="64" customHeight="1">
       <c r="A260" s="8" t="inlineStr">
         <is>
-          <t>T-B15220B1</t>
+          <t>T-089091A6</t>
         </is>
       </c>
       <c r="B260" s="8" t="inlineStr">
         <is>
-          <t>Система менеджмента информационной безопасности</t>
+          <t>Совместное функционирование систем SOAR, SIEM и платформ обмена разведданными</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>КВОИ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>Система менеджмента информационной безопасности</t>
+          <t>Совместное функционирование систем SOAR, SIEM и платформ обмена разведданными</t>
         </is>
       </c>
       <c r="E260" s="8" t="inlineStr">
@@ -10960,34 +10676,34 @@
       </c>
       <c r="F260" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Система менеджмента информационной безопасности (3 часа лекции, 1 час тематическая дискуссия).</t>
+          <t>Тема 1. Совместное функционирование систем SOAR, SIEM и платформ обмена разведданными (2 часа лекции).</t>
         </is>
       </c>
       <c r="G260" s="8" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 9</t>
+          <t>Связь SOAR/TI/SIEM; таблица 2, строка 67</t>
         </is>
       </c>
     </row>
     <row r="261" ht="64" customHeight="1">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>T-5FC18368</t>
+          <t>T-A00F34B3</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>Системы сбора событий информационной безопасности</t>
+          <t>Создание комплексного плейбука с обогащением и ответными действиями</t>
         </is>
       </c>
       <c r="C261" s="9" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Системы сбора событий информационной безопасности</t>
+          <t>Создание комплексного плейбука с обогащением и ответными действиями</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
@@ -10997,34 +10713,34 @@
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>Тема 8. Системы сбора событий информационной безопасности (4 часа лекции).</t>
+          <t>Тема 7. Создание комплексного плейбука с обогащением и ответными действиями (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G261" s="9" t="inlineStr">
         <is>
-          <t>Настройка системы защиты информации организации; таблица 2, строка 24</t>
+          <t>Автоматизация обработки инцидентов; таблица 2, строка 65</t>
         </is>
       </c>
     </row>
     <row r="262" ht="64" customHeight="1">
       <c r="A262" s="8" t="inlineStr">
         <is>
-          <t>T-C32FEFB2</t>
+          <t>T-686A516E</t>
         </is>
       </c>
       <c r="B262" s="8" t="inlineStr">
         <is>
-          <t>Совместное использование протоколов IPv4 и IPv6</t>
+          <t>Создание сценария автоматизации и устранения угрозы. Поиск уязвимостей в изолированной среде</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>Совместное использование протоколов IPv4 и IPv6</t>
+          <t>Создание сценария автоматизации и устранения угрозы. Поиск уязвимостей в изолированной среде</t>
         </is>
       </c>
       <c r="E262" s="8" t="inlineStr">
@@ -11034,67 +10750,71 @@
       </c>
       <c r="F262" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Совместное использование протоколов IPv4 и IPv6 (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 4. Создание сценария автоматизации и устранения угрозы. Поиск уязвимостей в изолированной среде (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G262" s="8" t="inlineStr">
         <is>
-          <t>Маршрутизация. IPv4 и IPv6 адресация; таблица 2, строка 16</t>
+          <t>Сканирование уязвимостей, скрипты реагирования, скрипты для сбора логов; таблица 2, строка 32</t>
         </is>
       </c>
     </row>
     <row r="263" ht="64" customHeight="1">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>T-78EF094E</t>
+          <t>T-D65B56DA</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
         <is>
-          <t>Совместное функционирование систем SIEM, SOAR и TIP</t>
+          <t>Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук</t>
         </is>
       </c>
       <c r="C263" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="D263" s="9" t="inlineStr"/>
+          <t>РКИОК</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук</t>
+        </is>
+      </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>Добавлено из программы</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Совместное функционирование систем SIEM, SOAR и TIP (2 часа лекции).</t>
+          <t>Тема 7. Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G263" s="9" t="inlineStr">
         <is>
-          <t>Раздел VII SOAR, TIP – автоматизация реагирования.; программа, абзацы 212</t>
+          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 57</t>
         </is>
       </c>
     </row>
     <row r="264" ht="64" customHeight="1">
       <c r="A264" s="8" t="inlineStr">
         <is>
-          <t>T-089091A6</t>
+          <t>T-D65B56DA</t>
         </is>
       </c>
       <c r="B264" s="8" t="inlineStr">
         <is>
-          <t>Совместное функционирование систем SOAR, SIEM и платформ обмена разведданными</t>
+          <t>Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Совместное функционирование систем SOAR, SIEM и платформ обмена разведданными</t>
+          <t>Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук</t>
         </is>
       </c>
       <c r="E264" s="8" t="inlineStr">
@@ -11104,34 +10824,34 @@
       </c>
       <c r="F264" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Совместное функционирование систем SOAR, SIEM и платформ обмена разведданными (2 часа лекции).</t>
+          <t>Тема 2. Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук (2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G264" s="8" t="inlineStr">
         <is>
-          <t>Связь SOAR/TI/SIEM; таблица 2, строка 67</t>
+          <t>Отработка практических заданий на базе киберполигона; таблица 2, строка 44</t>
         </is>
       </c>
     </row>
     <row r="265" ht="64" customHeight="1">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>T-A00F34B3</t>
+          <t>T-7FD25D51</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>Создание комплексного плейбука с обогащением и ответными действиями</t>
+          <t>Сопоставление событий с техниками MITRE ATT&amp;CK, построение цепочки действий злоумышленника, показ примеров атак и их последствий на базе киберполигона</t>
         </is>
       </c>
       <c r="C265" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>Создание комплексного плейбука с обогащением и ответными действиями</t>
+          <t>Сопоставление событий с техниками MITRE ATT&amp;CK, построение цепочки действий злоумышленника, показ примеров атак и их последствий на базе киберполигона</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
@@ -11141,34 +10861,34 @@
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Тема 7. Создание комплексного плейбука с обогащением и ответными действиями (2 часа практические занятия).</t>
+          <t>Тема 4. Сопоставление событий с техниками MITRE ATT&amp;CK, построение цепочки действий злоумышленника, показ примеров атак и их последствий на базе киберполигона (3 часа практические занятия).</t>
         </is>
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация обработки инцидентов; таблица 2, строка 65</t>
+          <t>Защита конечных устройств; таблица 2, строка 41</t>
         </is>
       </c>
     </row>
     <row r="266" ht="64" customHeight="1">
       <c r="A266" s="8" t="inlineStr">
         <is>
-          <t>T-686A516E</t>
+          <t>T-8EEE0E81</t>
         </is>
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>Создание сценария автоматизации и устранения угрозы. Поиск уязвимостей в изолированной среде</t>
+          <t>Списки управления доступом</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>Создание сценария автоматизации и устранения угрозы. Поиск уязвимостей в изолированной среде</t>
+          <t>Списки управления доступом</t>
         </is>
       </c>
       <c r="E266" s="8" t="inlineStr">
@@ -11178,24 +10898,24 @@
       </c>
       <c r="F266" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Создание сценария автоматизации и устранения угрозы. Поиск уязвимостей в изолированной среде (2 часа практические занятия).</t>
+          <t>Тема 8. Списки управления доступом (2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G266" s="8" t="inlineStr">
         <is>
-          <t>Сканирование уязвимостей, скрипты реагирования, скрипты для сбора логов; таблица 2, строка 32</t>
+          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 20</t>
         </is>
       </c>
     </row>
     <row r="267" ht="64" customHeight="1">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>T-D65B56DA</t>
+          <t>T-E8666CD3</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
         <is>
-          <t>Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук</t>
+          <t>Средства защиты: антивирусное ПО, брандмауэры, EDR, XDR, UEBA</t>
         </is>
       </c>
       <c r="C267" s="9" t="inlineStr">
@@ -11205,44 +10925,44 @@
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Базовая конфигурация TIP</t>
+          <t>Средства защиты: антивирусное ПО, брандмауэры, EDR, XDR, UEBA</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>Название отличается</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук (2 часа практические занятия).</t>
+          <t>Тема 1. Средства защиты: антивирусное ПО, брандмауэры, EDR, XDR, UEBA (2 часа лекции).</t>
         </is>
       </c>
       <c r="G267" s="9" t="inlineStr">
         <is>
-          <t>Отработка практических заданий на базе киберполигона; таблица 2, строка 45</t>
+          <t>Защита конечных устройств; таблица 2, строка 38</t>
         </is>
       </c>
     </row>
     <row r="268" ht="64" customHeight="1">
       <c r="A268" s="8" t="inlineStr">
         <is>
-          <t>T-D65B56DA</t>
+          <t>T-F5742C06</t>
         </is>
       </c>
       <c r="B268" s="8" t="inlineStr">
         <is>
-          <t>Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук</t>
+          <t>Средства криптографической защиты информации</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ККС</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук</t>
+          <t>Средства криптографической защиты информации</t>
         </is>
       </c>
       <c r="E268" s="8" t="inlineStr">
@@ -11252,71 +10972,71 @@
       </c>
       <c r="F268" s="8" t="inlineStr">
         <is>
-          <t>Тема 7. Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук (2 часа практические занятия).</t>
+          <t>Тема 2. Средства криптографической защиты информации (1 час лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G268" s="8" t="inlineStr">
         <is>
-          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 57</t>
+          <t>Криптографическая защита информации; таблица 2, строка 26</t>
         </is>
       </c>
     </row>
     <row r="269" ht="64" customHeight="1">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>T-7FD25D51</t>
+          <t>T-F5742C06</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
         <is>
-          <t>Сопоставление событий с техниками MITRE ATT&amp;CK, построение цепочки действий злоумышленника, показ примеров атак и их последствий на базе киберполигона</t>
+          <t>Средства криптографической защиты информации</t>
         </is>
       </c>
       <c r="C269" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Сопоставление событий с техниками MITRE ATT&amp;CK, построение цепочки действий злоумышленника, показ примеров атак и их последствий на базе киберполигона</t>
+          <t>Криптографические средства защиты информации</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>Точное соответствие</t>
+          <t>Название отличается</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Сопоставление событий с техниками MITRE ATT&amp;CK, построение цепочки действий злоумышленника, показ примеров атак и их последствий на базе киберполигона (3 часа практические занятия).</t>
+          <t>Тема 1. Средства криптографической защиты информации (2 часа лекции).</t>
         </is>
       </c>
       <c r="G269" s="9" t="inlineStr">
         <is>
-          <t>Защита конечных устройств; таблица 2, строка 42</t>
+          <t>Криптографическая защита информации.; таблица 2, строка 23</t>
         </is>
       </c>
     </row>
     <row r="270" ht="64" customHeight="1">
       <c r="A270" s="8" t="inlineStr">
         <is>
-          <t>T-8EEE0E81</t>
+          <t>T-F5742C06</t>
         </is>
       </c>
       <c r="B270" s="8" t="inlineStr">
         <is>
-          <t>Списки управления доступом</t>
+          <t>Средства криптографической защиты информации</t>
         </is>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>Списки управления доступом</t>
+          <t>Криптографические средства защиты информации</t>
         </is>
       </c>
       <c r="E270" s="8" t="inlineStr">
@@ -11326,34 +11046,34 @@
       </c>
       <c r="F270" s="8" t="inlineStr">
         <is>
-          <t>Тема 8. Списки управления доступом (2 часа лабораторные занятия).</t>
+          <t>Тема 6. Криптографические средства защиты информации (4 часа лекции).</t>
         </is>
       </c>
       <c r="G270" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 20</t>
+          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 11</t>
         </is>
       </c>
     </row>
     <row r="271" ht="64" customHeight="1">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>T-E8666CD3</t>
+          <t>T-F5742C06</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
         <is>
-          <t>Средства защиты: антивирусное ПО, брандмауэры, EDR, XDR, UEBA</t>
+          <t>Средства криптографической защиты информации</t>
         </is>
       </c>
       <c r="C271" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Средства защиты: антивирусное ПО, брандмауэры, EDR, XDR, UEBA</t>
+          <t>Средства криптографической защиты информации</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
@@ -11363,34 +11083,34 @@
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Средства защиты: антивирусное ПО, брандмауэры, EDR, XDR, UEBA (2 часа лекции).</t>
+          <t>Тема 7. Средства криптографической защиты информации (4 часа лекции).</t>
         </is>
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
-          <t>Защита конечных устройств; таблица 2, строка 39</t>
+          <t>Основы обеспечения кибербезопасности; таблица 2, строка 24</t>
         </is>
       </c>
     </row>
     <row r="272" ht="64" customHeight="1">
       <c r="A272" s="8" t="inlineStr">
         <is>
-          <t>T-F5742C06</t>
+          <t>T-10FDD2AB</t>
         </is>
       </c>
       <c r="B272" s="8" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации</t>
+          <t>Средства технической защиты информации</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>АКБ</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации</t>
+          <t>Средства технической защиты информации</t>
         </is>
       </c>
       <c r="E272" s="8" t="inlineStr">
@@ -11400,71 +11120,71 @@
       </c>
       <c r="F272" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Средства криптографической защиты информации (1 час лекции, 1 час круглый стол).</t>
+          <t>Тема 2. Средства технической защиты информации (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G272" s="8" t="inlineStr">
         <is>
-          <t>Криптографическая защита информации; таблица 2, строка 26</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
     <row r="273" ht="64" customHeight="1">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>T-F5742C06</t>
+          <t>T-10FDD2AB</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации</t>
+          <t>Средства технической защиты информации</t>
         </is>
       </c>
       <c r="C273" s="9" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Криптографические средства защиты информации</t>
+          <t>Средства технической защиты информации</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>Название отличается</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Средства криптографической защиты информации (2 часа лекции).</t>
+          <t>Тема 2. Средства технической защиты информации (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G273" s="9" t="inlineStr">
         <is>
-          <t>Криптографическая защита информации.; таблица 2, строка 23</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="274" ht="64" customHeight="1">
       <c r="A274" s="8" t="inlineStr">
         <is>
-          <t>T-F5742C06</t>
+          <t>T-10FDD2AB</t>
         </is>
       </c>
       <c r="B274" s="8" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации</t>
+          <t>Средства технической защиты информации</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>ЗИКС</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Криптографические средства защиты информации</t>
+          <t>Средства технической защиты информации</t>
         </is>
       </c>
       <c r="E274" s="8" t="inlineStr">
@@ -11474,34 +11194,34 @@
       </c>
       <c r="F274" s="8" t="inlineStr">
         <is>
-          <t>Тема 6. Криптографические средства защиты информации (4 часа лекции).</t>
+          <t>Тема 2. Средства технической защиты информации (3 часа лекции, 1 час круглый стол).</t>
         </is>
       </c>
       <c r="G274" s="8" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 11</t>
+          <t>Проектирование, создание и аттестация систем защиты информации.; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="275" ht="64" customHeight="1">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>T-F5742C06</t>
+          <t>T-10FDD2AB</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации</t>
+          <t>Средства технической защиты информации</t>
         </is>
       </c>
       <c r="C275" s="9" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ККС</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации</t>
+          <t>Средства технической защиты информации</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
@@ -11511,12 +11231,12 @@
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Тема 7. Средства криптографической защиты информации (4 часа лекции).</t>
+          <t>Тема 7. Средства технической защиты информации (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G275" s="9" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности; таблица 2, строка 24</t>
+          <t>Технические меры по обеспечению кибербезопасности; таблица 2, строка 21</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11253,7 @@
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>АКБ</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
@@ -11548,34 +11268,34 @@
       </c>
       <c r="F276" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Средства технической защиты информации (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 6. Средства технической защиты информации (4 часа лекции).</t>
         </is>
       </c>
       <c r="G276" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 13</t>
+          <t>Основы обеспечения кибербезопасности; таблица 2, строка 23</t>
         </is>
       </c>
     </row>
     <row r="277" ht="64" customHeight="1">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>T-10FDD2AB</t>
+          <t>T-CA997851</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
         <is>
-          <t>Средства технической защиты информации</t>
+          <t>Сценарии анализа: вредоносные IP, домены, хэши</t>
         </is>
       </c>
       <c r="C277" s="9" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Средства технической защиты информации</t>
+          <t>Сценарии анализа: вредоносные IP, домены, хэши</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
@@ -11585,34 +11305,34 @@
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Средства технической защиты информации (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 6. Сценарии анализа: вредоносные IP, домены, хэши (1 час лекции).</t>
         </is>
       </c>
       <c r="G277" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 10</t>
+          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 56</t>
         </is>
       </c>
     </row>
     <row r="278" ht="64" customHeight="1">
       <c r="A278" s="8" t="inlineStr">
         <is>
-          <t>T-10FDD2AB</t>
+          <t>T-F9900139</t>
         </is>
       </c>
       <c r="B278" s="8" t="inlineStr">
         <is>
-          <t>Средства технической защиты информации</t>
+          <t>Технические средства защиты информации</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>ЗИКС</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Средства технической защиты информации</t>
+          <t>Технические средства защиты информации</t>
         </is>
       </c>
       <c r="E278" s="8" t="inlineStr">
@@ -11622,34 +11342,34 @@
       </c>
       <c r="F278" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Средства технической защиты информации (3 часа лекции, 1 час круглый стол).</t>
+          <t>Тема 5. Технические средства защиты информации (4 часа лекции).</t>
         </is>
       </c>
       <c r="G278" s="8" t="inlineStr">
         <is>
-          <t>Проектирование, создание и аттестация систем защиты информации.; таблица 2, строка 10</t>
+          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="279" ht="64" customHeight="1">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>T-10FDD2AB</t>
+          <t>T-AC32D2AB</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
         <is>
-          <t>Средства технической защиты информации</t>
+          <t>Технические средства защиты информации. Проблемы безопасности беспроводных сетей и интернета вещей</t>
         </is>
       </c>
       <c r="C279" s="9" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Средства технической защиты информации</t>
+          <t>Технические средства защиты информации. Проблемы безопасности беспроводных сетей и интернета вещей</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
@@ -11659,34 +11379,34 @@
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Тема 7. Средства технической защиты информации (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 4. Технические средства защиты информации. Проблемы безопасности беспроводных сетей и интернета вещей (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G279" s="9" t="inlineStr">
         <is>
-          <t>Технические меры по обеспечению кибербезопасности; таблица 2, строка 21</t>
+          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 16</t>
         </is>
       </c>
     </row>
     <row r="280" ht="64" customHeight="1">
       <c r="A280" s="8" t="inlineStr">
         <is>
-          <t>T-10FDD2AB</t>
+          <t>T-91C88926</t>
         </is>
       </c>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>Средства технической защиты информации</t>
+          <t>Технологии организации VPN-туннелей</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>Средства технической защиты информации</t>
+          <t>Технологии организации VPN-туннелей</t>
         </is>
       </c>
       <c r="E280" s="8" t="inlineStr">
@@ -11696,34 +11416,34 @@
       </c>
       <c r="F280" s="8" t="inlineStr">
         <is>
-          <t>Тема 6. Средства технической защиты информации (4 часа лекции).</t>
+          <t>Тема 6. Технологии организации VPN-туннелей (2 часа лекции, 2 круглый стол).</t>
         </is>
       </c>
       <c r="G280" s="8" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности; таблица 2, строка 23</t>
+          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 18</t>
         </is>
       </c>
     </row>
     <row r="281" ht="64" customHeight="1">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>T-CA997851</t>
+          <t>T-56CB2759</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
         <is>
-          <t>Сценарии анализа: вредоносные IP, домены, хэши</t>
+          <t>Технологии трансляции IP-адресов</t>
         </is>
       </c>
       <c r="C281" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Сценарии анализа: вредоносные IP, домены, хэши</t>
+          <t>Технологии трансляции IP-адресов</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
@@ -11733,34 +11453,34 @@
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Тема 6. Сценарии анализа: вредоносные IP, домены, хэши (1 час лекции).</t>
+          <t>Тема 3. Технологии трансляции IP-адресов (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G281" s="9" t="inlineStr">
         <is>
-          <t>Интеграция и использование TI в ЦКБ; таблица 2, строка 56</t>
+          <t>Маршрутизация. IPv4 и IPv6 адресация; таблица 2, строка 17</t>
         </is>
       </c>
     </row>
     <row r="282" ht="64" customHeight="1">
       <c r="A282" s="8" t="inlineStr">
         <is>
-          <t>T-F9900139</t>
+          <t>T-13F397A0</t>
         </is>
       </c>
       <c r="B282" s="8" t="inlineStr">
         <is>
-          <t>Технические средства защиты информации</t>
+          <t>Технологии электронной цифровой подписи</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>ККС</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>Технические средства защиты информации</t>
+          <t>Технологии электронной цифровой подписи</t>
         </is>
       </c>
       <c r="E282" s="8" t="inlineStr">
@@ -11770,34 +11490,34 @@
       </c>
       <c r="F282" s="8" t="inlineStr">
         <is>
-          <t>Тема 5. Технические средства защиты информации (4 часа лекции).</t>
+          <t>Тема 3. Технологии электронной цифровой подписи (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 10</t>
+          <t>Криптографическая защита информации; таблица 2, строка 27</t>
         </is>
       </c>
     </row>
     <row r="283" ht="64" customHeight="1">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>T-AC32D2AB</t>
+          <t>T-1A43E6C1</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
         <is>
-          <t>Технические средства защиты информации. Проблемы безопасности беспроводных сетей и интернета вещей</t>
+          <t>Технология изоляции Sandbox</t>
         </is>
       </c>
       <c r="C283" s="9" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Технические средства защиты информации. Проблемы безопасности беспроводных сетей и интернета вещей</t>
+          <t>Технология изоляции Sandbox</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
@@ -11807,34 +11527,34 @@
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Технические средства защиты информации. Проблемы безопасности беспроводных сетей и интернета вещей (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 3. Технология изоляции Sandbox (1 час лекции).</t>
         </is>
       </c>
       <c r="G283" s="9" t="inlineStr">
         <is>
-          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 16</t>
+          <t>Защита конечных устройств; таблица 2, строка 40</t>
         </is>
       </c>
     </row>
     <row r="284" ht="64" customHeight="1">
       <c r="A284" s="8" t="inlineStr">
         <is>
-          <t>T-91C88926</t>
+          <t>T-89E9A90C</t>
         </is>
       </c>
       <c r="B284" s="8" t="inlineStr">
         <is>
-          <t>Технологии организации VPN-туннелей</t>
+          <t>Типовые плейбуки: фишинг, заражённый хост, подозрительная активность</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Технологии организации VPN-туннелей</t>
+          <t>Типовые плейбуки: фишинг, заражённый хост, подозрительная активность</t>
         </is>
       </c>
       <c r="E284" s="8" t="inlineStr">
@@ -11844,34 +11564,34 @@
       </c>
       <c r="F284" s="8" t="inlineStr">
         <is>
-          <t>Тема 6. Технологии организации VPN-туннелей (2 часа лекции, 2 круглый стол).</t>
+          <t>Тема 5. Типовые плейбуки: фишинг, заражённый хост, подозрительная активность (1 час лекции).</t>
         </is>
       </c>
       <c r="G284" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 18</t>
+          <t>Интеграция и использование SOAR в ЦКБ; таблица 2, строка 47</t>
         </is>
       </c>
     </row>
     <row r="285" ht="64" customHeight="1">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>T-56CB2759</t>
+          <t>T-9ED88B73</t>
         </is>
       </c>
       <c r="B285" s="9" t="inlineStr">
         <is>
-          <t>Технологии трансляции IP-адресов</t>
+          <t>Типовые сценарии интеграции</t>
         </is>
       </c>
       <c r="C285" s="9" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Технологии трансляции IP-адресов</t>
+          <t>Типовые сценарии интеграции</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
@@ -11881,34 +11601,34 @@
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Технологии трансляции IP-адресов (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 3. Типовые сценарии интеграции (1 час лекции).</t>
         </is>
       </c>
       <c r="G285" s="9" t="inlineStr">
         <is>
-          <t>Маршрутизация. IPv4 и IPv6 адресация; таблица 2, строка 17</t>
+          <t>Интеграция и использование SOAR в ЦКБ; таблица 2, строка 45</t>
         </is>
       </c>
     </row>
     <row r="286" ht="64" customHeight="1">
       <c r="A286" s="8" t="inlineStr">
         <is>
-          <t>T-13F397A0</t>
+          <t>T-A838C311</t>
         </is>
       </c>
       <c r="B286" s="8" t="inlineStr">
         <is>
-          <t>Технологии электронной цифровой подписи</t>
+          <t>Типы TI: стратегическая, тактическая, оперативная, техническая</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>РКИОК</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Технологии электронной цифровой подписи</t>
+          <t>Типы TI: стратегическая, тактическая, оперативная, техническая</t>
         </is>
       </c>
       <c r="E286" s="8" t="inlineStr">
@@ -11918,24 +11638,24 @@
       </c>
       <c r="F286" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Технологии электронной цифровой подписи (2 часа лекции, 2 часа круглый стол).</t>
+          <t>Тема 6. Типы TI: стратегическая, тактическая, оперативная, техническая (1 час лекции).</t>
         </is>
       </c>
       <c r="G286" s="8" t="inlineStr">
         <is>
-          <t>Криптографическая защита информации; таблица 2, строка 27</t>
+          <t>Введение в SOAR и TI; таблица 2, строка 39</t>
         </is>
       </c>
     </row>
     <row r="287" ht="64" customHeight="1">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>T-1A43E6C1</t>
+          <t>T-01727FC2</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
         <is>
-          <t>Технология изоляции Sandbox</t>
+          <t>Типы источников событий информационной безопасности. Теоретические аспекты подключения источников событий ИБ в SIEM (события Windows/Linux, СУБД, телекоммуникационного оборудования, антивируса, NGFW с функцией ips)</t>
         </is>
       </c>
       <c r="C287" s="9" t="inlineStr">
@@ -11945,7 +11665,7 @@
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Технология изоляции Sandbox</t>
+          <t>Типы источников событий информационной безопасности. Теоретические аспекты подключения источников событий ИБ к SIEM-системе (события Windows/Linux, СУБД, телекоммуникационного оборудования, антивируса, NGFW с функцией IPS)</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
@@ -11955,34 +11675,34 @@
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Технология изоляции Sandbox (1 час лекции).</t>
+          <t>Тема 3. Типы источников событий информационной безопасности. Теоретические аспекты подключения источников событий ИБ к SIEM-системе (события Windows/Linux, СУБД, телекоммуникационного оборудования, антивируса, NGFW с функцией ips) (1 час лекции).</t>
         </is>
       </c>
       <c r="G287" s="9" t="inlineStr">
         <is>
-          <t>Защита конечных устройств; таблица 2, строка 41</t>
+          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 29</t>
         </is>
       </c>
     </row>
     <row r="288" ht="64" customHeight="1">
       <c r="A288" s="8" t="inlineStr">
         <is>
-          <t>T-89E9A90C</t>
+          <t>T-0DC470E6</t>
         </is>
       </c>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>Типовые плейбуки: фишинг, заражённый хост, подозрительная активность</t>
+          <t>Топология сети при использовании межсетевых экранов</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Типовые плейбуки: фишинг, заражённый хост, подозрительная активность</t>
+          <t>Топология сети при использовании межсетевых экранов</t>
         </is>
       </c>
       <c r="E288" s="8" t="inlineStr">
@@ -11992,34 +11712,34 @@
       </c>
       <c r="F288" s="8" t="inlineStr">
         <is>
-          <t>Тема 5. Типовые плейбуки: фишинг, заражённый хост, подозрительная активность (1 час лекции).</t>
+          <t>Тема 10. Топология сети при использовании межсетевых экранов (2 часа лекции, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G288" s="8" t="inlineStr">
         <is>
-          <t>Интеграция и использование SOAR в ЦКБ; таблица 2, строка 47</t>
+          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 22</t>
         </is>
       </c>
     </row>
     <row r="289" ht="64" customHeight="1">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>T-9ED88B73</t>
+          <t>T-42D3BA79</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
         <is>
-          <t>Типовые сценарии интеграции</t>
+          <t>Требования безопасности к средствам криптографической защиты информации</t>
         </is>
       </c>
       <c r="C289" s="9" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>КЗИ</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Типовые сценарии интеграции</t>
+          <t>Требования безопасности к средствам криптографической защиты информации</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
@@ -12029,34 +11749,34 @@
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Типовые сценарии интеграции (1 час лекции).</t>
+          <t>Тема 4. Требования безопасности к средствам криптографической защиты информации (4 часа лекции).</t>
         </is>
       </c>
       <c r="G289" s="9" t="inlineStr">
         <is>
-          <t>Интеграция и использование SOAR в ЦКБ; таблица 2, строка 45</t>
+          <t>Средства криптографической защиты информации; таблица 2, строка 16</t>
         </is>
       </c>
     </row>
     <row r="290" ht="64" customHeight="1">
       <c r="A290" s="8" t="inlineStr">
         <is>
-          <t>T-A838C311</t>
+          <t>T-AED659CE</t>
         </is>
       </c>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t>Типы TI: стратегическая, тактическая, оперативная, техническая</t>
+          <t>Требования к системам защиты информации</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>РКИОК</t>
+          <t>АКБ</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Типы TI: стратегическая, тактическая, оперативная, техническая</t>
+          <t>Требования к системам защиты информации</t>
         </is>
       </c>
       <c r="E290" s="8" t="inlineStr">
@@ -12066,71 +11786,71 @@
       </c>
       <c r="F290" s="8" t="inlineStr">
         <is>
-          <t>Тема 6. Типы TI: стратегическая, тактическая, оперативная, техническая (1 час лекции).</t>
+          <t>Тема 1. Требования к системам защиты информации (9 часов лекции, 3 часа круглый стол).</t>
         </is>
       </c>
       <c r="G290" s="8" t="inlineStr">
         <is>
-          <t>Введение в SOAR и TI; таблица 2, строка 39</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 12</t>
         </is>
       </c>
     </row>
     <row r="291" ht="64" customHeight="1">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>T-01727FC2</t>
+          <t>T-AED659CE</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
         <is>
-          <t>Типы источников событий информационной безопасности. Теоретические аспекты подключения источников событий ИБ в SIEM (события Windows/Linux, СУБД, телекоммуникационного оборудования, антивируса, NGFW с функцией ips)</t>
+          <t>Требования к системам защиты информации</t>
         </is>
       </c>
       <c r="C291" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ЗИКС</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Типы источников событий информационной безопасности. Теоретические аспекты подключения источников событий ИБ в SIEM (события Windows/Linux, СУБД, телекоммуникационного оборудования, антивируса, NGFW с функцией ips)</t>
+          <t>Требования к системам защиты информации</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>Название отличается</t>
+          <t>Точное соответствие</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Типы источников событий информационной безопасности. Теоретические аспекты подключения источников событий ИБ к SIEM-системе (события Windows/Linux, СУБД, телекоммуникационного оборудования, антивируса, NGFW с функцией ips) (1 час лекции).</t>
+          <t>Тема 1. Требования к системам защиты информации (8 часов лекции, 4 часа круглый стол).</t>
         </is>
       </c>
       <c r="G291" s="9" t="inlineStr">
         <is>
-          <t>Системы управления информационной безопасностью и событиями безопасности (SIEM); таблица 2, строка 30</t>
+          <t>Проектирование, создание и аттестация систем защиты информации.; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="292" ht="64" customHeight="1">
       <c r="A292" s="8" t="inlineStr">
         <is>
-          <t>T-0DC470E6</t>
+          <t>T-FB249971</t>
         </is>
       </c>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t>Топология сети при использовании межсетевых экранов</t>
+          <t>Требования к системам защиты информации. Аттестация систем защиты информации</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Топология сети при использовании межсетевых экранов</t>
+          <t>Требования к системам защиты информации. Аттестация систем защиты информации</t>
         </is>
       </c>
       <c r="E292" s="8" t="inlineStr">
@@ -12140,34 +11860,34 @@
       </c>
       <c r="F292" s="8" t="inlineStr">
         <is>
-          <t>Тема 10. Топология сети при использовании межсетевых экранов (2 часа лекции, 2 часа лабораторные занятия).</t>
+          <t>Тема 5. Требования к системам защиты информации. Аттестация систем защиты информации (6 часов лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G292" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 22</t>
+          <t>Основы обеспечения кибербезопасности; таблица 2, строка 22</t>
         </is>
       </c>
     </row>
     <row r="293" ht="64" customHeight="1">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>T-42D3BA79</t>
+          <t>T-4C9FADFD</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
         <is>
-          <t>Требования безопасности к средствам криптографической защиты информации</t>
+          <t>Требования к системам защиты информации для типовых информационных систем</t>
         </is>
       </c>
       <c r="C293" s="9" t="inlineStr">
         <is>
-          <t>КЗИ</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Требования безопасности к средствам криптографической защиты информации</t>
+          <t>Требования к системам защиты информации для типовых информационных систем</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
@@ -12177,34 +11897,34 @@
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Требования безопасности к средствам криптографической защиты информации (4 часа лекции).</t>
+          <t>Тема 2. Требования к системам защиты информации для типовых информационных систем (4 часа лекции).</t>
         </is>
       </c>
       <c r="G293" s="9" t="inlineStr">
         <is>
-          <t>Средства криптографической защиты информации; таблица 2, строка 16</t>
+          <t>Проектирование системы защиты информации организации; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="294" ht="64" customHeight="1">
       <c r="A294" s="8" t="inlineStr">
         <is>
-          <t>T-AED659CE</t>
+          <t>T-B2AE2A95</t>
         </is>
       </c>
       <c r="B294" s="8" t="inlineStr">
         <is>
-          <t>Требования к системам защиты информации</t>
+          <t>Требования к системе защиты информации информационных систем</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>АКБ</t>
+          <t>КВОИ</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Требования к системам защиты информации</t>
+          <t>Требования к системе защиты информации информационных систем</t>
         </is>
       </c>
       <c r="E294" s="8" t="inlineStr">
@@ -12214,34 +11934,34 @@
       </c>
       <c r="F294" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Требования к системам защиты информации (9 часов лекции, 3 часа круглый стол).</t>
+          <t>Тема 2. Требования к системе защиты информации информационных систем (2 часа лекции).</t>
         </is>
       </c>
       <c r="G294" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 12</t>
+          <t>Практические аспекты обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 14</t>
         </is>
       </c>
     </row>
     <row r="295" ht="64" customHeight="1">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>T-AED659CE</t>
+          <t>T-615AA328</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
         <is>
-          <t>Требования к системам защиты информации</t>
+          <t>Требования по кибербезопасности</t>
         </is>
       </c>
       <c r="C295" s="9" t="inlineStr">
         <is>
-          <t>ЗИКС</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Требования к системам защиты информации</t>
+          <t>Требования по кибербезопасности</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
@@ -12251,34 +11971,34 @@
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Требования к системам защиты информации (8 часов лекции, 4 часа круглый стол).</t>
+          <t>Тема 1. Требования по кибербезопасности (6 часов лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G295" s="9" t="inlineStr">
         <is>
-          <t>Проектирование, создание и аттестация систем защиты информации.; таблица 2, строка 9</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="296" ht="64" customHeight="1">
       <c r="A296" s="8" t="inlineStr">
         <is>
-          <t>T-FB249971</t>
+          <t>T-615AA328</t>
         </is>
       </c>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t>Требования к системам защиты информации. Аттестация систем защиты информации</t>
+          <t>Требования по кибербезопасности</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>Требования к системам защиты информации. Аттестация систем защиты информации</t>
+          <t>Требования по кибербезопасности</t>
         </is>
       </c>
       <c r="E296" s="8" t="inlineStr">
@@ -12288,34 +12008,34 @@
       </c>
       <c r="F296" s="8" t="inlineStr">
         <is>
-          <t>Тема 5. Требования к системам защиты информации. Аттестация систем защиты информации (6 часов лекции, 2 часа круглый стол).</t>
+          <t>Тема 1. Требования по кибербезопасности (6 часов лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G296" s="8" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности; таблица 2, строка 22</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="297" ht="64" customHeight="1">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>T-4C9FADFD</t>
+          <t>T-615AA328</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
         <is>
-          <t>Требования к системам защиты информации для типовых информационных систем</t>
+          <t>Требования по кибербезопасности</t>
         </is>
       </c>
       <c r="C297" s="9" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>ЗИОЗ</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Требования к системам защиты информации для типовых информационных систем</t>
+          <t>Требования по кибербезопасности</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
@@ -12325,24 +12045,24 @@
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Требования к системам защиты информации для типовых информационных систем (4 часа лекции).</t>
+          <t>Тема 1. Требования по кибербезопасности (6 часов лекции, 2 часа тематическая дискуссия).</t>
         </is>
       </c>
       <c r="G297" s="9" t="inlineStr">
         <is>
-          <t>Проектирование системы защиты информации организации; таблица 2, строка 10</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
     <row r="298" ht="64" customHeight="1">
       <c r="A298" s="8" t="inlineStr">
         <is>
-          <t>T-B2AE2A95</t>
+          <t>T-615AA328</t>
         </is>
       </c>
       <c r="B298" s="8" t="inlineStr">
         <is>
-          <t>Требования к системе защиты информации информационных систем</t>
+          <t>Требования по кибербезопасности</t>
         </is>
       </c>
       <c r="C298" s="8" t="inlineStr">
@@ -12352,7 +12072,7 @@
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>Требования к системе защиты информации информационных систем</t>
+          <t>Требования по кибербезопасности</t>
         </is>
       </c>
       <c r="E298" s="8" t="inlineStr">
@@ -12362,12 +12082,12 @@
       </c>
       <c r="F298" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Требования к системе защиты информации информационных систем (2 часа лекции).</t>
+          <t>Тема 1. Требования по кибербезопасности (2 часа лекции).</t>
         </is>
       </c>
       <c r="G298" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 14</t>
+          <t>Практические аспекты обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12104,7 @@
       </c>
       <c r="C299" s="9" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>ТЗПД</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
@@ -12399,34 +12119,34 @@
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Требования по кибербезопасности (6 часов лекции, 2 часа круглый стол).</t>
+          <t>Тема 1. Требования по кибербезопасности (6 часов лекции, 2 часа тематическая дискуссия).</t>
         </is>
       </c>
       <c r="G299" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 9</t>
+          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 14</t>
         </is>
       </c>
     </row>
     <row r="300" ht="64" customHeight="1">
       <c r="A300" s="8" t="inlineStr">
         <is>
-          <t>T-615AA328</t>
+          <t>T-41BAC61B</t>
         </is>
       </c>
       <c r="B300" s="8" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности</t>
+          <t>Требования по кибербезопасности объектов информационной инфраструктуры государственных органов и иных организаций</t>
         </is>
       </c>
       <c r="C300" s="8" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности</t>
+          <t>Требования по кибербезопасности объектов информационной инфраструктуры государственных органов и иных организаций</t>
         </is>
       </c>
       <c r="E300" s="8" t="inlineStr">
@@ -12436,34 +12156,34 @@
       </c>
       <c r="F300" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Требования по кибербезопасности (6 часов лекции, 2 часа круглый стол).</t>
+          <t>Тема 3. Требования по кибербезопасности объектов информационной инфраструктуры государственных органов и иных организаций (2 часа лекции).</t>
         </is>
       </c>
       <c r="G300" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 15</t>
+          <t>Нормативное правовое регулирование вопросов кибербезопасности в Республике Беларусь; таблица 2, строка 8</t>
         </is>
       </c>
     </row>
     <row r="301" ht="64" customHeight="1">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>T-615AA328</t>
+          <t>T-7D4709CE</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности</t>
+          <t>Тренды киберпреступности. Кибератаки с использованием методов социальной инженерии</t>
         </is>
       </c>
       <c r="C301" s="9" t="inlineStr">
         <is>
-          <t>ЗИОЗ</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности</t>
+          <t>Тренды киберпреступности. Кибератаки с использованием методов социальной инженерии</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
@@ -12473,34 +12193,34 @@
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Требования по кибербезопасности (6 часов лекции, 2 часа тематическая дискуссия).</t>
+          <t>Тема 1. Тренды киберпреступности. Кибератаки с использованием методов социальной инженерии (4 часа лекции).</t>
         </is>
       </c>
       <c r="G301" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 13</t>
+          <t>Тренды киберпреступности. Кибератаки с использованием методов социальной инженерии.; таблица 2, строка 11</t>
         </is>
       </c>
     </row>
     <row r="302" ht="64" customHeight="1">
       <c r="A302" s="8" t="inlineStr">
         <is>
-          <t>T-615AA328</t>
+          <t>T-D2A4FAE7</t>
         </is>
       </c>
       <c r="B302" s="8" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности</t>
+          <t>Управление киберинцидентами</t>
         </is>
       </c>
       <c r="C302" s="8" t="inlineStr">
         <is>
-          <t>КВОИ</t>
+          <t>АКБ</t>
         </is>
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности</t>
+          <t>Управление киберинцидентами</t>
         </is>
       </c>
       <c r="E302" s="8" t="inlineStr">
@@ -12510,34 +12230,34 @@
       </c>
       <c r="F302" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Требования по кибербезопасности (2 часа лекции).</t>
+          <t>Тема 1. Управление киберинцидентами (8 часов лекции, 4 часа круглый стол).</t>
         </is>
       </c>
       <c r="G302" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 13</t>
+          <t>Управление киберинцидентами; таблица 2, строка 20</t>
         </is>
       </c>
     </row>
     <row r="303" ht="64" customHeight="1">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>T-615AA328</t>
+          <t>T-D2A4FAE7</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности</t>
+          <t>Управление киберинцидентами</t>
         </is>
       </c>
       <c r="C303" s="9" t="inlineStr">
         <is>
-          <t>ТЗПД</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности</t>
+          <t>Управление киберинцидентами</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
@@ -12547,24 +12267,24 @@
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Требования по кибербезопасности (6 часов лекции, 2 часа тематическая дискуссия).</t>
+          <t>Тема 1. Управление киберинцидентами (6 часов лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G303" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности; таблица 2, строка 14</t>
+          <t>Управление киберинцидентами; таблица 2, строка 23</t>
         </is>
       </c>
     </row>
     <row r="304" ht="64" customHeight="1">
       <c r="A304" s="8" t="inlineStr">
         <is>
-          <t>T-41BAC61B</t>
+          <t>T-F2B40F58</t>
         </is>
       </c>
       <c r="B304" s="8" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности объектов информационной инфраструктуры государственных органов и иных организаций</t>
+          <t>Управление обновлениями и устранение уязвимостей</t>
         </is>
       </c>
       <c r="C304" s="8" t="inlineStr">
@@ -12574,7 +12294,7 @@
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>Требования по кибербезопасности объектов информационной инфраструктуры государственных органов и иных организаций</t>
+          <t>Управление обновлениями и устранение уязвимостей</t>
         </is>
       </c>
       <c r="E304" s="8" t="inlineStr">
@@ -12584,34 +12304,34 @@
       </c>
       <c r="F304" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Требования по кибербезопасности объектов информационной инфраструктуры государственных органов и иных организаций (2 часа лекции).</t>
+          <t>Тема 2. Управление обновлениями и устранение уязвимостей (2 часа лекции).</t>
         </is>
       </c>
       <c r="G304" s="8" t="inlineStr">
         <is>
-          <t>Нормативное правовое регулирование вопросов кибербезопасности в Республике Беларусь; таблица 2, строка 8</t>
+          <t>Защита конечных устройств; таблица 2, строка 39</t>
         </is>
       </c>
     </row>
     <row r="305" ht="64" customHeight="1">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>T-7D4709CE</t>
+          <t>T-2CAF7650</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
         <is>
-          <t>Тренды киберпреступности. Кибератаки с использованием методов социальной инженерии</t>
+          <t>Управление рисками кибербезопасности</t>
         </is>
       </c>
       <c r="C305" s="9" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>АКБ</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Тренды киберпреступности. Кибератаки с использованием методов социальной инженерии</t>
+          <t>Управление рисками кибербезопасности</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
@@ -12621,34 +12341,34 @@
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Тренды киберпреступности. Кибератаки с использованием методов социальной инженерии (4 часа лекции).</t>
+          <t>Тема 2. Управление рисками кибербезопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G305" s="9" t="inlineStr">
         <is>
-          <t>Тренды киберпреступности. Кибератаки с использованием методов социальной инженерии.; таблица 2, строка 11</t>
+          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="306" ht="64" customHeight="1">
       <c r="A306" s="8" t="inlineStr">
         <is>
-          <t>T-D2A4FAE7</t>
+          <t>T-2CAF7650</t>
         </is>
       </c>
       <c r="B306" s="8" t="inlineStr">
         <is>
-          <t>Управление киберинцидентами</t>
+          <t>Управление рисками кибербезопасности</t>
         </is>
       </c>
       <c r="C306" s="8" t="inlineStr">
         <is>
-          <t>АКБ</t>
+          <t>БКТ</t>
         </is>
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>Управление киберинцидентами</t>
+          <t>Управление рисками кибербезопасности</t>
         </is>
       </c>
       <c r="E306" s="8" t="inlineStr">
@@ -12658,34 +12378,34 @@
       </c>
       <c r="F306" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Управление киберинцидентами (8 часов лекции, 4 часа круглый стол).</t>
+          <t>Тема 2. Управление рисками кибербезопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G306" s="8" t="inlineStr">
         <is>
-          <t>Управление киберинцидентами; таблица 2, строка 20</t>
+          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 12</t>
         </is>
       </c>
     </row>
     <row r="307" ht="64" customHeight="1">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>T-D2A4FAE7</t>
+          <t>T-2CAF7650</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
         <is>
-          <t>Управление киберинцидентами</t>
+          <t>Управление рисками кибербезопасности</t>
         </is>
       </c>
       <c r="C307" s="9" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>ТЗПД</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Управление киберинцидентами</t>
+          <t>Управление рисками кибербезопасности</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
@@ -12695,34 +12415,34 @@
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Управление киберинцидентами (6 часов лекции, 2 часа круглый стол).</t>
+          <t>Тема 1. Управление рисками кибербезопасности (2 часа лекции).</t>
         </is>
       </c>
       <c r="G307" s="9" t="inlineStr">
         <is>
-          <t>Управление киберинцидентами; таблица 2, строка 23</t>
+          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 11</t>
         </is>
       </c>
     </row>
     <row r="308" ht="64" customHeight="1">
       <c r="A308" s="8" t="inlineStr">
         <is>
-          <t>T-F2B40F58</t>
+          <t>T-2CAF7650</t>
         </is>
       </c>
       <c r="B308" s="8" t="inlineStr">
         <is>
-          <t>Управление обновлениями и устранение уязвимостей</t>
+          <t>Управление рисками кибербезопасности</t>
         </is>
       </c>
       <c r="C308" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>Управление обновлениями и устранение уязвимостей</t>
+          <t>Управление рисками кибербезопасности</t>
         </is>
       </c>
       <c r="E308" s="8" t="inlineStr">
@@ -12732,34 +12452,34 @@
       </c>
       <c r="F308" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Управление обновлениями и устранение уязвимостей (2 часа лекции).</t>
+          <t>Тема 1. Управление рисками кибербезопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G308" s="8" t="inlineStr">
         <is>
-          <t>Защита конечных устройств; таблица 2, строка 40</t>
+          <t>Методологические основы обеспечения кибербезопасности корпоративных систем; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="309" ht="64" customHeight="1">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>T-2CAF7650</t>
+          <t>T-306E1D90</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности</t>
+          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="C309" s="9" t="inlineStr">
         <is>
-          <t>АКБ</t>
+          <t>ЗИКС</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности</t>
+          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
@@ -12769,34 +12489,34 @@
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>Тема 2. Управление рисками кибербезопасности (4 часа лекции).</t>
+          <t>Тема 5. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (6 часов лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G309" s="9" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 10</t>
+          <t>Обеспечение функционирования системы защиты информации в процессе эксплуатации информационной системы.; таблица 2, строка 18</t>
         </is>
       </c>
     </row>
     <row r="310" ht="64" customHeight="1">
       <c r="A310" s="8" t="inlineStr">
         <is>
-          <t>T-2CAF7650</t>
+          <t>T-306E1D90</t>
         </is>
       </c>
       <c r="B310" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности</t>
+          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="C310" s="8" t="inlineStr">
         <is>
-          <t>БКТ</t>
+          <t>ККС</t>
         </is>
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности</t>
+          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="E310" s="8" t="inlineStr">
@@ -12806,34 +12526,34 @@
       </c>
       <c r="F310" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Управление рисками кибербезопасности (4 часа лекции).</t>
+          <t>Тема 4. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G310" s="8" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 12</t>
+          <t>Правовые и организационные меры по обеспечению кибербезопасности; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
     <row r="311" ht="64" customHeight="1">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>T-2CAF7650</t>
+          <t>T-306E1D90</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности</t>
+          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="C311" s="9" t="inlineStr">
         <is>
-          <t>ТЗПД</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности</t>
+          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
@@ -12843,34 +12563,34 @@
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Управление рисками кибербезопасности (2 часа лекции).</t>
+          <t>Тема 1. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G311" s="9" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 11</t>
+          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
     <row r="312" ht="64" customHeight="1">
       <c r="A312" s="8" t="inlineStr">
         <is>
-          <t>T-2CAF7650</t>
+          <t>T-306E1D90</t>
         </is>
       </c>
       <c r="B312" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности</t>
+          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="C312" s="8" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности</t>
+          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
         </is>
       </c>
       <c r="E312" s="8" t="inlineStr">
@@ -12880,12 +12600,12 @@
       </c>
       <c r="F312" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Управление рисками кибербезопасности (4 часа лекции).</t>
+          <t>Тема 8. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G312" s="8" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности корпоративных систем; таблица 2, строка 9</t>
+          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 13</t>
         </is>
       </c>
     </row>
@@ -12902,7 +12622,7 @@
       </c>
       <c r="C313" s="9" t="inlineStr">
         <is>
-          <t>ЗИКС</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
@@ -12917,34 +12637,34 @@
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Тема 5. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (6 часов лекции, 2 часа круглый стол).</t>
+          <t>Тема 3. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (4 часа лекции).</t>
         </is>
       </c>
       <c r="G313" s="9" t="inlineStr">
         <is>
-          <t>Обеспечение функционирования системы защиты информации в процессе эксплуатации информационной системы.; таблица 2, строка 18</t>
+          <t>Основы обеспечения кибербезопасности; таблица 2, строка 20</t>
         </is>
       </c>
     </row>
     <row r="314" ht="64" customHeight="1">
       <c r="A314" s="8" t="inlineStr">
         <is>
-          <t>T-306E1D90</t>
+          <t>T-ABB5DBDC</t>
         </is>
       </c>
       <c r="B314" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
+          <t>Управление рисками кибербезопасности в сфере здравоохранения</t>
         </is>
       </c>
       <c r="C314" s="8" t="inlineStr">
         <is>
-          <t>ККС</t>
+          <t>ЗИОЗ</t>
         </is>
       </c>
       <c r="D314" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
+          <t>Управление рисками кибербезопасности в сфере здравоохранения</t>
         </is>
       </c>
       <c r="E314" s="8" t="inlineStr">
@@ -12954,34 +12674,34 @@
       </c>
       <c r="F314" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (4 часа лекции).</t>
+          <t>Тема 2. Управление рисками кибербезопасности в сфере здравоохранения (2 часа лекции).</t>
         </is>
       </c>
       <c r="G314" s="8" t="inlineStr">
         <is>
-          <t>Правовые и организационные меры по обеспечению кибербезопасности; таблица 2, строка 13</t>
+          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="315" ht="64" customHeight="1">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>T-306E1D90</t>
+          <t>T-CBD50885</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
+          <t>Управление рисками кибербезопасности, корректирующие и превентивные действия, контроль выполнения принятых мер</t>
         </is>
       </c>
       <c r="C315" s="9" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>АУРИК</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
+          <t>Управление рисками кибербезопасности, корректирующие и превентивные действия, контроль выполнения принятых мер</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
@@ -12991,34 +12711,34 @@
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (4 часа лекции).</t>
+          <t>Тема 1. Управление рисками кибербезопасности, корректирующие и превентивные действия, контроль выполнения принятых мер (6 часов лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G315" s="9" t="inlineStr">
         <is>
-          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 13</t>
+          <t>Управление рисками кибербезопасности; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="316" ht="64" customHeight="1">
       <c r="A316" s="8" t="inlineStr">
         <is>
-          <t>T-306E1D90</t>
+          <t>T-195D56B5</t>
         </is>
       </c>
       <c r="B316" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
+          <t>Управление рисками кибербезопасности на критически важных объектах информатизации</t>
         </is>
       </c>
       <c r="C316" s="8" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>КВОИ</t>
         </is>
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
+          <t>Управление рисками кибербезопасности на критически важных объектах информатизации</t>
         </is>
       </c>
       <c r="E316" s="8" t="inlineStr">
@@ -13028,34 +12748,34 @@
       </c>
       <c r="F316" s="8" t="inlineStr">
         <is>
-          <t>Тема 8. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (4 часа лекции).</t>
+          <t>Тема 2. Управление рисками кибербезопасности на критически важных объектах информатизации (1 час лекции, 1 час тематическая дискуссия).</t>
         </is>
       </c>
       <c r="G316" s="8" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 13</t>
+          <t>Методологические основы обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 10</t>
         </is>
       </c>
     </row>
     <row r="317" ht="64" customHeight="1">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>T-306E1D90</t>
+          <t>T-7E0D748E</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
+          <t>Управление рисками, уязвимостями, угрозами</t>
         </is>
       </c>
       <c r="C317" s="9" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности</t>
+          <t>Управление рисками, уязвимостями, угрозами</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
@@ -13065,34 +12785,34 @@
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Управление рисками кибербезопасности. Аудиты в области обеспечения кибербезопасности (4 часа лекции).</t>
+          <t>Тема 3. Управление рисками, уязвимостями, угрозами (3 часа лекции).</t>
         </is>
       </c>
       <c r="G317" s="9" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности; таблица 2, строка 20</t>
+          <t>Основные функции центров обеспечения кибербезопасности и реагирования на киберинциденты объектов информационной инфраструктуры государственных органов и иных организаций (ЦКБ), процессы информационной безопасности; таблица 2, строка 16</t>
         </is>
       </c>
     </row>
     <row r="318" ht="64" customHeight="1">
       <c r="A318" s="8" t="inlineStr">
         <is>
-          <t>T-ABB5DBDC</t>
+          <t>T-5DAB8241</t>
         </is>
       </c>
       <c r="B318" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности в сфере здравоохранения</t>
+          <t>Управление уязвимостями информационных систем</t>
         </is>
       </c>
       <c r="C318" s="8" t="inlineStr">
         <is>
-          <t>ЗИОЗ</t>
+          <t>ПСАЭ</t>
         </is>
       </c>
       <c r="D318" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности в сфере здравоохранения</t>
+          <t>Управление уязвимостями информационных систем</t>
         </is>
       </c>
       <c r="E318" s="8" t="inlineStr">
@@ -13102,34 +12822,34 @@
       </c>
       <c r="F318" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Управление рисками кибербезопасности в сфере здравоохранения (2 часа лекции).</t>
+          <t>Тема 4. Управление уязвимостями информационных систем (4 часа лекции).</t>
         </is>
       </c>
       <c r="G318" s="8" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности; таблица 2, строка 10</t>
+          <t>Настройка системы защиты информации организации; таблица 2, строка 20</t>
         </is>
       </c>
     </row>
     <row r="319" ht="64" customHeight="1">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>T-CBD50885</t>
+          <t>T-F5496B09</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности, корректирующие и превентивные действия, контроль выполнения принятых мер</t>
+          <t>Уязвимости DHCP и DNS протоколов</t>
         </is>
       </c>
       <c r="C319" s="9" t="inlineStr">
         <is>
-          <t>АУРИК</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности, корректирующие и превентивные действия, контроль выполнения принятых мер</t>
+          <t>Уязвимости DHCP и DNS протоколов</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
@@ -13139,34 +12859,34 @@
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Управление рисками кибербезопасности, корректирующие и превентивные действия, контроль выполнения принятых мер (6 часов лекции, 2 часа круглый стол).</t>
+          <t>Тема 3. Уязвимости DHCP и DNS протоколов (2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G319" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности; таблица 2, строка 15</t>
+          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="320" ht="64" customHeight="1">
       <c r="A320" s="8" t="inlineStr">
         <is>
-          <t>T-195D56B5</t>
+          <t>T-1CEFEBB1</t>
         </is>
       </c>
       <c r="B320" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности на критически важных объектах информатизации</t>
+          <t>Уязвимости виртуальных локальных сетей</t>
         </is>
       </c>
       <c r="C320" s="8" t="inlineStr">
         <is>
-          <t>КВОИ</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>Управление рисками кибербезопасности на критически важных объектах информатизации</t>
+          <t>Уязвимости виртуальных локальных сетей</t>
         </is>
       </c>
       <c r="E320" s="8" t="inlineStr">
@@ -13176,34 +12896,34 @@
       </c>
       <c r="F320" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Управление рисками кибербезопасности на критически важных объектах информатизации (1 час лекции, 1 час тематическая дискуссия).</t>
+          <t>Тема 4. Уязвимости виртуальных локальных сетей (2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G320" s="8" t="inlineStr">
         <is>
-          <t>Методологические основы обеспечения кибербезопасности критически важных объектов информатизации; таблица 2, строка 10</t>
+          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 16</t>
         </is>
       </c>
     </row>
     <row r="321" ht="64" customHeight="1">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>T-7E0D748E</t>
+          <t>T-17A5CA4D</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками, уязвимостями, угрозами</t>
+          <t>Уязвимости объектов информационной инфраструктуры</t>
         </is>
       </c>
       <c r="C321" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Управление рисками, уязвимостями, угрозами</t>
+          <t>Уязвимости объектов информационной инфраструктуры</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
@@ -13213,34 +12933,34 @@
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Управление рисками, уязвимостями, угрозами (3 часа лекции).</t>
+          <t>Тема 4. Уязвимости объектов информационной инфраструктуры (2 часа лекции, 4 часа практические занятия, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G321" s="9" t="inlineStr">
         <is>
-          <t>Основные функции центров обеспечения кибербезопасности и реагирования на киберинциденты объектов информационной инфраструктуры государственных органов и иных организаций (ЦКБ), процессы информационной безопасности; таблица 2, строка 16</t>
+          <t>Основы обеспечения кибербезопасности; таблица 2, строка 21</t>
         </is>
       </c>
     </row>
     <row r="322" ht="64" customHeight="1">
       <c r="A322" s="8" t="inlineStr">
         <is>
-          <t>T-5DAB8241</t>
+          <t>T-B5070575</t>
         </is>
       </c>
       <c r="B322" s="8" t="inlineStr">
         <is>
-          <t>Управление уязвимостями информационных систем</t>
+          <t>Уязвимости объектов информационной инфраструктуры и их активов</t>
         </is>
       </c>
       <c r="C322" s="8" t="inlineStr">
         <is>
-          <t>ПСАЭ</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D322" s="8" t="inlineStr">
         <is>
-          <t>Управление уязвимостями информационных систем</t>
+          <t>Уязвимости объектов информационной инфраструктуры и их активов</t>
         </is>
       </c>
       <c r="E322" s="8" t="inlineStr">
@@ -13250,34 +12970,34 @@
       </c>
       <c r="F322" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Управление уязвимостями информационных систем (4 часа лекции).</t>
+          <t>Тема 3. Уязвимости объектов информационной инфраструктуры и их активов (8 часов практические занятия).</t>
         </is>
       </c>
       <c r="G322" s="8" t="inlineStr">
         <is>
-          <t>Настройка системы защиты информации организации; таблица 2, строка 20</t>
+          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 15</t>
         </is>
       </c>
     </row>
     <row r="323" ht="64" customHeight="1">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>T-F5496B09</t>
+          <t>T-B5070575</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
         <is>
-          <t>Уязвимости DHCP и DNS протоколов</t>
+          <t>Уязвимости объектов информационной инфраструктуры и их активов</t>
         </is>
       </c>
       <c r="C323" s="9" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>ОКМ</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Уязвимости DHCP и DNS протоколов</t>
+          <t>Уязвимости объектов информационной инфраструктуры и их активов</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
@@ -13287,34 +13007,34 @@
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>Тема 3. Уязвимости DHCP и DNS протоколов (2 часа лабораторные занятия).</t>
+          <t>Тема 4. Уязвимости объектов информационной инфраструктуры и их активов (4 часа лекции, 4 часа практические занятия, 2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G323" s="9" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 15</t>
+          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 9</t>
         </is>
       </c>
     </row>
     <row r="324" ht="64" customHeight="1">
       <c r="A324" s="8" t="inlineStr">
         <is>
-          <t>T-1CEFEBB1</t>
+          <t>T-1878B180</t>
         </is>
       </c>
       <c r="B324" s="8" t="inlineStr">
         <is>
-          <t>Уязвимости виртуальных локальных сетей</t>
+          <t>Физическая инфраструктура: коммутаторы, концентраторы, кабельные среды</t>
         </is>
       </c>
       <c r="C324" s="8" t="inlineStr">
         <is>
-          <t>ТК</t>
+          <t>ОПКС</t>
         </is>
       </c>
       <c r="D324" s="8" t="inlineStr">
         <is>
-          <t>Уязвимости виртуальных локальных сетей</t>
+          <t>Физическая инфраструктура: коммутаторы, концентраторы, кабельные среды</t>
         </is>
       </c>
       <c r="E324" s="8" t="inlineStr">
@@ -13324,34 +13044,34 @@
       </c>
       <c r="F324" s="8" t="inlineStr">
         <is>
-          <t>Тема 4. Уязвимости виртуальных локальных сетей (2 часа лабораторные занятия).</t>
+          <t>Тема 2. Физическая инфраструктура: коммутаторы, концентраторы, кабельные среды (2 часа лабораторные занятия).</t>
         </is>
       </c>
       <c r="G324" s="8" t="inlineStr">
         <is>
-          <t>Практические аспекты обеспечения кибербезопасности корпоративных систем; таблица 2, строка 16</t>
+          <t>Основы построения компьютерных сетей; таблица 2, строка 7</t>
         </is>
       </c>
     </row>
     <row r="325" ht="64" customHeight="1">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>T-17A5CA4D</t>
+          <t>T-9F71AF66</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
         <is>
-          <t>Уязвимости объектов информационной инфраструктуры</t>
+          <t>Цели и задачи SOAR, отличия от SIEM и взаимодействие с ним, роль автоматизации</t>
         </is>
       </c>
       <c r="C325" s="9" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>Уязвимости объектов информационной инфраструктуры</t>
+          <t>Цели и задачи SOAR, отличия от SIEM и взаимодействие с ним, роль автоматизации</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
@@ -13361,34 +13081,34 @@
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Уязвимости объектов информационной инфраструктуры (2 часа лекции, 4 часа практические занятия, 2 часа лабораторные занятия).</t>
+          <t>Тема 1. Цели и задачи SOAR, отличия от SIEM и взаимодействие с ним, роль автоматизации (2 часа лекции, 2 часа практические занятия).</t>
         </is>
       </c>
       <c r="G325" s="9" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности; таблица 2, строка 21</t>
+          <t>SOAR, TIP - Автоматизация реагирования; таблица 2, строка 34</t>
         </is>
       </c>
     </row>
     <row r="326" ht="64" customHeight="1">
       <c r="A326" s="8" t="inlineStr">
         <is>
-          <t>T-B5070575</t>
+          <t>T-A4326792</t>
         </is>
       </c>
       <c r="B326" s="8" t="inlineStr">
         <is>
-          <t>Уязвимости объектов информационной инфраструктуры и их активов</t>
+          <t>Цель и задачи TIP, назначение и функции, интеграция с системами</t>
         </is>
       </c>
       <c r="C326" s="8" t="inlineStr">
         <is>
-          <t>КО</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D326" s="8" t="inlineStr">
         <is>
-          <t>Уязвимости объектов информационной инфраструктуры и их активов</t>
+          <t>Цель и задачи TIP, назначение и функции, интеграция с системами</t>
         </is>
       </c>
       <c r="E326" s="8" t="inlineStr">
@@ -13398,34 +13118,34 @@
       </c>
       <c r="F326" s="8" t="inlineStr">
         <is>
-          <t>Тема 3. Уязвимости объектов информационной инфраструктуры и их активов (8 часов практические занятия).</t>
+          <t>Тема 2. Цель и задачи TIP, назначение и функции, интеграция с системами (2 часа лекции).</t>
         </is>
       </c>
       <c r="G326" s="8" t="inlineStr">
         <is>
-          <t>Меры по обеспечению кибербезопасности.; таблица 2, строка 15</t>
+          <t>SOAR, TIP - Автоматизация реагирования; таблица 2, строка 35</t>
         </is>
       </c>
     </row>
     <row r="327" ht="64" customHeight="1">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>T-B5070575</t>
+          <t>T-6DB4AB9E</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
         <is>
-          <t>Уязвимости объектов информационной инфраструктуры и их активов</t>
+          <t>Цифровая трансформация как новый этап развития государства и общества</t>
         </is>
       </c>
       <c r="C327" s="9" t="inlineStr">
         <is>
-          <t>ОКМ</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>Уязвимости объектов информационной инфраструктуры и их активов</t>
+          <t>Цифровая трансформация как новый этап развития государства и общества</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
@@ -13435,34 +13155,34 @@
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>Тема 4. Уязвимости объектов информационной инфраструктуры и их активов (4 часа лекции, 4 часа практические занятия, 2 часа лабораторные занятия).</t>
+          <t>Тема 1. Цифровая трансформация как новый этап развития государства и общества (2 часа лекции).</t>
         </is>
       </c>
       <c r="G327" s="9" t="inlineStr">
         <is>
-          <t>Основы обеспечения кибербезопасности. Законодательство в области обеспечения кибербезопасности; таблица 2, строка 9</t>
+          <t>Стратегия государства: экономика данных и цифровое государство (2026–2030); таблица 2, строка 6</t>
         </is>
       </c>
     </row>
     <row r="328" ht="64" customHeight="1">
       <c r="A328" s="8" t="inlineStr">
         <is>
-          <t>T-1878B180</t>
+          <t>T-E2E0EC86</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
         <is>
-          <t>Физическая инфраструктура: коммутаторы, концентраторы, кабельные среды</t>
+          <t>Цифровой суверенитет: импортонезависимость и отечественная цифровая экосистема</t>
         </is>
       </c>
       <c r="C328" s="8" t="inlineStr">
         <is>
-          <t>ОПКС</t>
+          <t>ЦТГУ</t>
         </is>
       </c>
       <c r="D328" s="8" t="inlineStr">
         <is>
-          <t>Физическая инфраструктура: коммутаторы, концентраторы, кабельные среды</t>
+          <t>Цифровой суверенитет: импортонезависимость и отечественная цифровая экосистема</t>
         </is>
       </c>
       <c r="E328" s="8" t="inlineStr">
@@ -13472,34 +13192,34 @@
       </c>
       <c r="F328" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Физическая инфраструктура: коммутаторы, концентраторы, кабельные среды (2 часа лабораторные занятия).</t>
+          <t>Тема 1. Цифровой суверенитет: импортонезависимость и отечественная цифровая экосистема (2 часа лекции).</t>
         </is>
       </c>
       <c r="G328" s="8" t="inlineStr">
         <is>
-          <t>Основы построения компьютерных сетей; таблица 2, строка 7</t>
+          <t>Цифровой суверенитет и информационная безопасность; таблица 2, строка 16</t>
         </is>
       </c>
     </row>
     <row r="329" ht="64" customHeight="1">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>T-9F71AF66</t>
+          <t>T-93960566</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
         <is>
-          <t>Цели и задачи SOAR, отличия от SIEM и взаимодействие с ним, роль автоматизации</t>
+          <t>Эксплуатация активов информационных систем. Администратор кибербезопасности</t>
         </is>
       </c>
       <c r="C329" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ЗИКС</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Цели и задачи SOAR, отличия от SIEM и взаимодействие с ним, роль автоматизации</t>
+          <t>Эксплуатация активов информационных систем. Администратор кибербезопасности</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
@@ -13509,34 +13229,34 @@
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>Тема 1. Цели и задачи SOAR, отличия от SIEM и взаимодействие с ним, роль автоматизации (2 часа лекции, 2 часа практические занятия).</t>
+          <t>Тема 3. Эксплуатация активов информационных систем. Администратор кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
         </is>
       </c>
       <c r="G329" s="9" t="inlineStr">
         <is>
-          <t>SOAR, TIP, XDR- Автоматизация реагирования; таблица 2, строка 35</t>
+          <t>Обеспечение функционирования системы защиты информации в процессе эксплуатации информационной системы.; таблица 2, строка 16</t>
         </is>
       </c>
     </row>
     <row r="330" ht="64" customHeight="1">
       <c r="A330" s="8" t="inlineStr">
         <is>
-          <t>T-A4326792</t>
+          <t>T-78FBD05D</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
         <is>
-          <t>Цель и задачи TIP, назначение и функции, интеграция с системами</t>
+          <t>Электронная цифровая подпись</t>
         </is>
       </c>
       <c r="C330" s="8" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>ТК</t>
         </is>
       </c>
       <c r="D330" s="8" t="inlineStr">
         <is>
-          <t>Цель и задачи TIP, назначение и функции, интеграция с системами</t>
+          <t>Электронная цифровая подпись</t>
         </is>
       </c>
       <c r="E330" s="8" t="inlineStr">
@@ -13546,67 +13266,71 @@
       </c>
       <c r="F330" s="8" t="inlineStr">
         <is>
-          <t>Тема 2. Цель и задачи TIP, назначение и функции, интеграция с системами (2 часа лекции).</t>
+          <t>Тема 2. Электронная цифровая подпись (4 часа лекции).</t>
         </is>
       </c>
       <c r="G330" s="8" t="inlineStr">
         <is>
-          <t>SOAR, TIP, XDR- Автоматизация реагирования; таблица 2, строка 36</t>
+          <t>Особенности криптографической защиты информации; таблица 2, строка 26</t>
         </is>
       </c>
     </row>
     <row r="331" ht="64" customHeight="1">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>T-A505DFF7</t>
+          <t>T-FDFBBC6A</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
         <is>
-          <t>Цель и задачи XDR, его преимущества</t>
+          <t>Электронные документы и электронная цифровая подпись</t>
         </is>
       </c>
       <c r="C331" s="9" t="inlineStr">
         <is>
-          <t>ОКБО</t>
+          <t>КО</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>Цель и задачи XDR, его преимущества</t>
+          <t>Электронные документы и электронная цифровая подпись</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>Описание не найдено</t>
-        </is>
-      </c>
-      <c r="F331" s="9" t="inlineStr"/>
+          <t>Точное соответствие</t>
+        </is>
+      </c>
+      <c r="F331" s="9" t="inlineStr">
+        <is>
+          <t>Тема 2. Электронные документы и электронная цифровая подпись (2 часа лекции).</t>
+        </is>
+      </c>
       <c r="G331" s="9" t="inlineStr">
         <is>
-          <t>SOAR, TIP, XDR- Автоматизация реагирования; таблица 2, строка 37</t>
+          <t>Криптографическая защита информации.; таблица 2, строка 24</t>
         </is>
       </c>
     </row>
     <row r="332" ht="64" customHeight="1">
       <c r="A332" s="8" t="inlineStr">
         <is>
-          <t>T-6DB4AB9E</t>
+          <t>T-E90F5F72</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
         <is>
-          <t>Цифровая трансформация как новый этап развития государства и общества</t>
+          <t>Этапы действий ЦКБ: мониторинг, обнаружение, анализ, реагирование, восстановление</t>
         </is>
       </c>
       <c r="C332" s="8" t="inlineStr">
         <is>
-          <t>ЦТГУ</t>
+          <t>ОКБО</t>
         </is>
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>Цифровая трансформация как новый этап развития государства и общества</t>
+          <t>Этапы действий ЦКБ: мониторинг, обнаружение, анализ, реагирование, восстановление</t>
         </is>
       </c>
       <c r="E332" s="8" t="inlineStr">
@@ -13616,195 +13340,10 @@
       </c>
       <c r="F332" s="8" t="inlineStr">
         <is>
-          <t>Тема 1. Цифровая трансформация как новый этап развития государства и общества (2 часа лекции).</t>
+          <t>Тема 4. Этапы действий ЦКБ: мониторинг, обнаружение, анализ, реагирование, восстановление (3 часа лекции).</t>
         </is>
       </c>
       <c r="G332" s="8" t="inlineStr">
-        <is>
-          <t>Стратегия государства: экономика данных и цифровое государство (2026–2030); таблица 2, строка 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="333" ht="64" customHeight="1">
-      <c r="A333" s="9" t="inlineStr">
-        <is>
-          <t>T-E2E0EC86</t>
-        </is>
-      </c>
-      <c r="B333" s="9" t="inlineStr">
-        <is>
-          <t>Цифровой суверенитет: импортонезависимость и отечественная цифровая экосистема</t>
-        </is>
-      </c>
-      <c r="C333" s="9" t="inlineStr">
-        <is>
-          <t>ЦТГУ</t>
-        </is>
-      </c>
-      <c r="D333" s="9" t="inlineStr">
-        <is>
-          <t>Цифровой суверенитет: импортонезависимость и отечественная цифровая экосистема</t>
-        </is>
-      </c>
-      <c r="E333" s="9" t="inlineStr">
-        <is>
-          <t>Точное соответствие</t>
-        </is>
-      </c>
-      <c r="F333" s="9" t="inlineStr">
-        <is>
-          <t>Тема 1. Цифровой суверенитет: импортонезависимость и отечественная цифровая экосистема (2 часа лекции).</t>
-        </is>
-      </c>
-      <c r="G333" s="9" t="inlineStr">
-        <is>
-          <t>Цифровой суверенитет и информационная безопасность; таблица 2, строка 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="334" ht="64" customHeight="1">
-      <c r="A334" s="8" t="inlineStr">
-        <is>
-          <t>T-93960566</t>
-        </is>
-      </c>
-      <c r="B334" s="8" t="inlineStr">
-        <is>
-          <t>Эксплуатация активов информационных систем. Администратор кибербезопасности</t>
-        </is>
-      </c>
-      <c r="C334" s="8" t="inlineStr">
-        <is>
-          <t>ЗИКС</t>
-        </is>
-      </c>
-      <c r="D334" s="8" t="inlineStr">
-        <is>
-          <t>Эксплуатация активов информационных систем. Администратор кибербезопасности</t>
-        </is>
-      </c>
-      <c r="E334" s="8" t="inlineStr">
-        <is>
-          <t>Точное соответствие</t>
-        </is>
-      </c>
-      <c r="F334" s="8" t="inlineStr">
-        <is>
-          <t>Тема 3. Эксплуатация активов информационных систем. Администратор кибербезопасности (2 часа лекции, 2 часа круглый стол).</t>
-        </is>
-      </c>
-      <c r="G334" s="8" t="inlineStr">
-        <is>
-          <t>Обеспечение функционирования системы защиты информации в процессе эксплуатации информационной системы.; таблица 2, строка 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="335" ht="64" customHeight="1">
-      <c r="A335" s="9" t="inlineStr">
-        <is>
-          <t>T-78FBD05D</t>
-        </is>
-      </c>
-      <c r="B335" s="9" t="inlineStr">
-        <is>
-          <t>Электронная цифровая подпись</t>
-        </is>
-      </c>
-      <c r="C335" s="9" t="inlineStr">
-        <is>
-          <t>ТК</t>
-        </is>
-      </c>
-      <c r="D335" s="9" t="inlineStr">
-        <is>
-          <t>Электронная цифровая подпись</t>
-        </is>
-      </c>
-      <c r="E335" s="9" t="inlineStr">
-        <is>
-          <t>Точное соответствие</t>
-        </is>
-      </c>
-      <c r="F335" s="9" t="inlineStr">
-        <is>
-          <t>Тема 2. Электронная цифровая подпись (4 часа лекции).</t>
-        </is>
-      </c>
-      <c r="G335" s="9" t="inlineStr">
-        <is>
-          <t>Особенности криптографической защиты информации; таблица 2, строка 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="336" ht="64" customHeight="1">
-      <c r="A336" s="8" t="inlineStr">
-        <is>
-          <t>T-FDFBBC6A</t>
-        </is>
-      </c>
-      <c r="B336" s="8" t="inlineStr">
-        <is>
-          <t>Электронные документы и электронная цифровая подпись</t>
-        </is>
-      </c>
-      <c r="C336" s="8" t="inlineStr">
-        <is>
-          <t>КО</t>
-        </is>
-      </c>
-      <c r="D336" s="8" t="inlineStr">
-        <is>
-          <t>Электронные документы и электронная цифровая подпись</t>
-        </is>
-      </c>
-      <c r="E336" s="8" t="inlineStr">
-        <is>
-          <t>Точное соответствие</t>
-        </is>
-      </c>
-      <c r="F336" s="8" t="inlineStr">
-        <is>
-          <t>Тема 2. Электронные документы и электронная цифровая подпись (2 часа лекции).</t>
-        </is>
-      </c>
-      <c r="G336" s="8" t="inlineStr">
-        <is>
-          <t>Криптографическая защита информации.; таблица 2, строка 24</t>
-        </is>
-      </c>
-    </row>
-    <row r="337" ht="64" customHeight="1">
-      <c r="A337" s="9" t="inlineStr">
-        <is>
-          <t>T-E90F5F72</t>
-        </is>
-      </c>
-      <c r="B337" s="9" t="inlineStr">
-        <is>
-          <t>Этапы действий ЦКБ: мониторинг, обнаружение, анализ, реагирование, восстановление</t>
-        </is>
-      </c>
-      <c r="C337" s="9" t="inlineStr">
-        <is>
-          <t>ОКБО</t>
-        </is>
-      </c>
-      <c r="D337" s="9" t="inlineStr">
-        <is>
-          <t>Этапы действий ЦКБ: мониторинг, обнаружение, анализ, реагирование, восстановление</t>
-        </is>
-      </c>
-      <c r="E337" s="9" t="inlineStr">
-        <is>
-          <t>Точное соответствие</t>
-        </is>
-      </c>
-      <c r="F337" s="9" t="inlineStr">
-        <is>
-          <t>Тема 4. Этапы действий ЦКБ: мониторинг, обнаружение, анализ, реагирование, восстановление (3 часа лекции).</t>
-        </is>
-      </c>
-      <c r="G337" s="9" t="inlineStr">
         <is>
           <t>Основные функции центров обеспечения кибербезопасности и реагирования на киберинциденты объектов информационной инфраструктуры государственных органов и иных организаций (ЦКБ), процессы информационной безопасности; таблица 2, строка 17</t>
         </is>
@@ -13837,7 +13376,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -14015,40 +13554,6 @@
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Смысловое соответствие; тексты программ сохранены</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="64" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Базовая конфигурация SOAR: написания плейбука, отработка плейбука, процесс автоматизации</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Сборка базового плейбука обработки фишинга. Создание визуального сценария реагирования</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Смысловое соответствие; тексты программ сохранены</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Базовая конфигурация TIP</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Создание фида угроз. Сценарий обогащения IOC через внешние источники. Интеграция TI в плейбук</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Смысловое соответствие; тексты программ сохранены</t>
         </is>
@@ -14749,12 +14254,12 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DD2K_roGc8IbIGYyaZz0ZyRB3WkjQpx2/view</t>
+          <t>https://drive.google.com/file/d/1bOUvJIn8iJR-cZNs_B-_NVS1Z9rSGipG/view</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>80da11e0b77f33f6df15e1eac8810beff94b93c60757e805b62cf3af21d2be7d</t>
+          <t>897cd177bd99455c64e4a293f84582fd1cade3e51e7d92aa965d9d4445587068</t>
         </is>
       </c>
     </row>
